--- a/research/traditional_assets/database/data/netherlands/netherlands_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_auto_parts.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09736887025547922</v>
+        <v>0.09715104857022008</v>
       </c>
       <c r="C2">
-        <v>340.1371406736428</v>
+        <v>336.9078467757705</v>
       </c>
       <c r="D2">
-        <v>258.5371406736427</v>
+        <v>258.9208467757705</v>
       </c>
       <c r="E2">
-        <v>-194.4</v>
+        <v>-190.787</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.613</v>
       </c>
       <c r="G2">
         <v>81.59999999999999</v>
@@ -1439,28 +1439,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1817339</v>
       </c>
       <c r="N2">
-        <v>22.02499999999999</v>
+        <v>21.84326609999999</v>
       </c>
       <c r="O2">
-        <v>5.682449999999998</v>
+        <v>5.635562653799997</v>
       </c>
       <c r="P2">
-        <v>16.34255</v>
+        <v>16.20770344619999</v>
       </c>
       <c r="Q2">
-        <v>47.94255</v>
+        <v>47.80770344619999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09736887025547922</v>
+        <v>0.09775537633355563</v>
       </c>
       <c r="T2">
-        <v>1.190966980496056</v>
+        <v>1.199893217865026</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>121.1936793300534</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09715104857022008</v>
+        <v>0.09693322688496094</v>
       </c>
       <c r="C3">
-        <v>336.9078467757705</v>
+        <v>333.679693520269</v>
       </c>
       <c r="D3">
-        <v>258.9208467757705</v>
+        <v>259.305693520269</v>
       </c>
       <c r="E3">
-        <v>-190.787</v>
+        <v>-187.174</v>
       </c>
       <c r="F3">
-        <v>3.613</v>
+        <v>7.226</v>
       </c>
       <c r="G3">
         <v>81.59999999999999</v>
@@ -1521,28 +1521,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M3">
-        <v>0.1817339</v>
+        <v>0.3634678</v>
       </c>
       <c r="N3">
-        <v>21.84326609999999</v>
+        <v>21.66153219999999</v>
       </c>
       <c r="O3">
-        <v>5.635562653799997</v>
+        <v>5.588675307599998</v>
       </c>
       <c r="P3">
-        <v>16.20770344619999</v>
+        <v>16.07285689239999</v>
       </c>
       <c r="Q3">
-        <v>47.80770344619999</v>
+        <v>47.67285689239999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09775537633355563</v>
+        <v>0.09814977029077647</v>
       </c>
       <c r="T3">
-        <v>1.199893217865026</v>
+        <v>1.209001623343568</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.1936793300534</v>
+        <v>60.5968396650267</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09693322688496094</v>
+        <v>0.0967154051997018</v>
       </c>
       <c r="C4">
-        <v>333.679693520269</v>
+        <v>330.4526860008872</v>
       </c>
       <c r="D4">
-        <v>259.305693520269</v>
+        <v>259.6916860008873</v>
       </c>
       <c r="E4">
-        <v>-187.174</v>
+        <v>-183.561</v>
       </c>
       <c r="F4">
-        <v>7.226</v>
+        <v>10.839</v>
       </c>
       <c r="G4">
         <v>81.59999999999999</v>
@@ -1603,28 +1603,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M4">
-        <v>0.3634678</v>
+        <v>0.5452017</v>
       </c>
       <c r="N4">
-        <v>21.66153219999999</v>
+        <v>21.47979829999999</v>
       </c>
       <c r="O4">
-        <v>5.588675307599998</v>
+        <v>5.541787961399998</v>
       </c>
       <c r="P4">
-        <v>16.07285689239999</v>
+        <v>15.93801033859999</v>
       </c>
       <c r="Q4">
-        <v>47.67285689239999</v>
+        <v>47.5380103386</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09814977029077647</v>
+        <v>0.09855229608216681</v>
       </c>
       <c r="T4">
-        <v>1.209001623343568</v>
+        <v>1.218297830996924</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.5968396650267</v>
+        <v>40.3978931100178</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0967154051997018</v>
+        <v>0.09649758351444267</v>
       </c>
       <c r="C5">
-        <v>330.4526860008872</v>
+        <v>327.2268293417491</v>
       </c>
       <c r="D5">
-        <v>259.6916860008873</v>
+        <v>260.0788293417491</v>
       </c>
       <c r="E5">
-        <v>-183.561</v>
+        <v>-179.948</v>
       </c>
       <c r="F5">
-        <v>10.839</v>
+        <v>14.452</v>
       </c>
       <c r="G5">
         <v>81.59999999999999</v>
@@ -1685,28 +1685,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M5">
-        <v>0.5452017</v>
+        <v>0.7269356</v>
       </c>
       <c r="N5">
-        <v>21.47979829999999</v>
+        <v>21.29806439999999</v>
       </c>
       <c r="O5">
-        <v>5.541787961399998</v>
+        <v>5.494900615199998</v>
       </c>
       <c r="P5">
-        <v>15.93801033859999</v>
+        <v>15.80316378479999</v>
       </c>
       <c r="Q5">
-        <v>47.5380103386</v>
+        <v>47.40316378479999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09855229608216681</v>
+        <v>0.09896320782754445</v>
       </c>
       <c r="T5">
-        <v>1.218297830996924</v>
+        <v>1.227787709643059</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.3978931100178</v>
+        <v>30.29841983251335</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09649758351444267</v>
+        <v>0.09627976182918352</v>
       </c>
       <c r="C6">
-        <v>327.2268293417491</v>
+        <v>324.0021286975795</v>
       </c>
       <c r="D6">
-        <v>260.0788293417491</v>
+        <v>260.4671286975795</v>
       </c>
       <c r="E6">
-        <v>-179.948</v>
+        <v>-176.335</v>
       </c>
       <c r="F6">
-        <v>14.452</v>
+        <v>18.065</v>
       </c>
       <c r="G6">
         <v>81.59999999999999</v>
@@ -1767,28 +1767,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M6">
-        <v>0.7269356</v>
+        <v>0.9086695</v>
       </c>
       <c r="N6">
-        <v>21.29806439999999</v>
+        <v>21.11633049999999</v>
       </c>
       <c r="O6">
-        <v>5.494900615199998</v>
+        <v>5.448013268999999</v>
       </c>
       <c r="P6">
-        <v>15.80316378479999</v>
+        <v>15.66831723099999</v>
       </c>
       <c r="Q6">
-        <v>47.40316378479999</v>
+        <v>47.268317231</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09896320782754445</v>
+        <v>0.09938277034650898</v>
       </c>
       <c r="T6">
-        <v>1.227787709643059</v>
+        <v>1.23747737520806</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.29841983251335</v>
+        <v>24.23873586601068</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09627976182918352</v>
+        <v>0.09606194014392438</v>
       </c>
       <c r="C7">
-        <v>324.0021286975795</v>
+        <v>320.7785892539338</v>
       </c>
       <c r="D7">
-        <v>260.4671286975795</v>
+        <v>260.8565892539338</v>
       </c>
       <c r="E7">
-        <v>-176.335</v>
+        <v>-172.722</v>
       </c>
       <c r="F7">
-        <v>18.065</v>
+        <v>21.678</v>
       </c>
       <c r="G7">
         <v>81.59999999999999</v>
@@ -1849,28 +1849,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M7">
-        <v>0.9086695</v>
+        <v>1.0904034</v>
       </c>
       <c r="N7">
-        <v>21.11633049999999</v>
+        <v>20.93459659999999</v>
       </c>
       <c r="O7">
-        <v>5.448013268999999</v>
+        <v>5.401125922799998</v>
       </c>
       <c r="P7">
-        <v>15.66831723099999</v>
+        <v>15.53347067719999</v>
       </c>
       <c r="Q7">
-        <v>47.268317231</v>
+        <v>47.13347067719999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09938277034650898</v>
+        <v>0.09981125972757914</v>
       </c>
       <c r="T7">
-        <v>1.23747737520806</v>
+        <v>1.247373203870188</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.23873586601068</v>
+        <v>20.1989465550089</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09606194014392438</v>
+        <v>0.09584411845866526</v>
       </c>
       <c r="C8">
-        <v>320.7785892539338</v>
+        <v>317.5562162274284</v>
       </c>
       <c r="D8">
-        <v>260.8565892539338</v>
+        <v>261.2472162274284</v>
       </c>
       <c r="E8">
-        <v>-172.722</v>
+        <v>-169.109</v>
       </c>
       <c r="F8">
-        <v>21.678</v>
+        <v>25.291</v>
       </c>
       <c r="G8">
         <v>81.59999999999999</v>
@@ -1931,28 +1931,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M8">
-        <v>1.0904034</v>
+        <v>1.2721373</v>
       </c>
       <c r="N8">
-        <v>20.93459659999999</v>
+        <v>20.75286269999999</v>
       </c>
       <c r="O8">
-        <v>5.401125922799998</v>
+        <v>5.354238576599998</v>
       </c>
       <c r="P8">
-        <v>15.53347067719999</v>
+        <v>15.39862412339999</v>
       </c>
       <c r="Q8">
-        <v>47.13347067719999</v>
+        <v>46.99862412339999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09981125972757914</v>
+        <v>0.1002489639340487</v>
       </c>
       <c r="T8">
-        <v>1.247373203870188</v>
+        <v>1.257481846051932</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.1989465550089</v>
+        <v>17.3133827614362</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09584411845866525</v>
+        <v>0.09562629677340613</v>
       </c>
       <c r="C9">
-        <v>317.5562162274284</v>
+        <v>314.3350148659734</v>
       </c>
       <c r="D9">
-        <v>261.2472162274284</v>
+        <v>261.6390148659734</v>
       </c>
       <c r="E9">
-        <v>-169.109</v>
+        <v>-165.496</v>
       </c>
       <c r="F9">
-        <v>25.291</v>
+        <v>28.904</v>
       </c>
       <c r="G9">
         <v>81.59999999999999</v>
@@ -2013,28 +2013,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M9">
-        <v>1.2721373</v>
+        <v>1.4538712</v>
       </c>
       <c r="N9">
-        <v>20.75286269999999</v>
+        <v>20.57112879999999</v>
       </c>
       <c r="O9">
-        <v>5.354238576599998</v>
+        <v>5.307351230399997</v>
       </c>
       <c r="P9">
-        <v>15.39862412339999</v>
+        <v>15.26377756959999</v>
       </c>
       <c r="Q9">
-        <v>46.99862412339999</v>
+        <v>46.86377756959999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1002489639340487</v>
+        <v>0.1006961834493545</v>
       </c>
       <c r="T9">
-        <v>1.257481846051932</v>
+        <v>1.267810241324584</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.3133827614362</v>
+        <v>15.14920991625667</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09562629677340613</v>
+        <v>0.09540847508814697</v>
       </c>
       <c r="C10">
-        <v>314.3350148659734</v>
+        <v>311.1149904490082</v>
       </c>
       <c r="D10">
-        <v>261.6390148659734</v>
+        <v>262.0319904490082</v>
       </c>
       <c r="E10">
-        <v>-165.496</v>
+        <v>-161.883</v>
       </c>
       <c r="F10">
-        <v>28.904</v>
+        <v>32.517</v>
       </c>
       <c r="G10">
         <v>81.59999999999999</v>
@@ -2095,28 +2095,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M10">
-        <v>1.4538712</v>
+        <v>1.6356051</v>
       </c>
       <c r="N10">
-        <v>20.57112879999999</v>
+        <v>20.38939489999999</v>
       </c>
       <c r="O10">
-        <v>5.307351230399997</v>
+        <v>5.260463884199998</v>
       </c>
       <c r="P10">
-        <v>15.26377756959999</v>
+        <v>15.12893101579999</v>
       </c>
       <c r="Q10">
-        <v>46.86377756959999</v>
+        <v>46.72893101579999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1006961834493545</v>
+        <v>0.1011532319649967</v>
       </c>
       <c r="T10">
-        <v>1.267810241324584</v>
+        <v>1.278365634295536</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.14920991625667</v>
+        <v>13.46596437000593</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09540847508814697</v>
+        <v>0.09530195340288786</v>
       </c>
       <c r="C11">
-        <v>311.1149904490082</v>
+        <v>307.6945980424772</v>
       </c>
       <c r="D11">
-        <v>262.0319904490082</v>
+        <v>262.2245980424772</v>
       </c>
       <c r="E11">
-        <v>-161.883</v>
+        <v>-158.27</v>
       </c>
       <c r="F11">
-        <v>32.517</v>
+        <v>36.13</v>
       </c>
       <c r="G11">
         <v>81.59999999999999</v>
@@ -2177,45 +2177,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M11">
-        <v>1.6356051</v>
+        <v>1.871534</v>
       </c>
       <c r="N11">
-        <v>20.38939489999999</v>
+        <v>20.15346599999999</v>
       </c>
       <c r="O11">
-        <v>5.260463884199998</v>
+        <v>5.199594227999998</v>
       </c>
       <c r="P11">
-        <v>15.12893101579999</v>
+        <v>14.95387177199999</v>
       </c>
       <c r="Q11">
-        <v>46.72893101579999</v>
+        <v>46.55387177199999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1011532319649967</v>
+        <v>0.1016204371143198</v>
       </c>
       <c r="T11">
-        <v>1.278365634295536</v>
+        <v>1.289155591554731</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.46596437000593</v>
+        <v>11.76842098513839</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09530195340288786</v>
+        <v>0.09509526171762869</v>
       </c>
       <c r="C12">
-        <v>307.6945980424772</v>
+        <v>304.4561373142491</v>
       </c>
       <c r="D12">
-        <v>262.2245980424772</v>
+        <v>262.5991373142491</v>
       </c>
       <c r="E12">
-        <v>-158.27</v>
+        <v>-154.657</v>
       </c>
       <c r="F12">
-        <v>36.13</v>
+        <v>39.743</v>
       </c>
       <c r="G12">
         <v>81.59999999999999</v>
@@ -2259,28 +2259,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M12">
-        <v>1.871534</v>
+        <v>2.0586874</v>
       </c>
       <c r="N12">
-        <v>20.15346599999999</v>
+        <v>19.96631259999999</v>
       </c>
       <c r="O12">
-        <v>5.199594227999998</v>
+        <v>5.151308650799998</v>
       </c>
       <c r="P12">
-        <v>14.95387177199999</v>
+        <v>14.81500394919999</v>
       </c>
       <c r="Q12">
-        <v>46.55387177199999</v>
+        <v>46.4150039492</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1016204371143198</v>
+        <v>0.1020981412557626</v>
       </c>
       <c r="T12">
-        <v>1.289155591554731</v>
+        <v>1.30018801976357</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.76842098513839</v>
+        <v>10.69856453194399</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09509526171762869</v>
+        <v>0.09503993803236958</v>
       </c>
       <c r="C13">
-        <v>304.4561373142491</v>
+        <v>300.9435691473312</v>
       </c>
       <c r="D13">
-        <v>262.5991373142491</v>
+        <v>262.6995691473313</v>
       </c>
       <c r="E13">
-        <v>-154.657</v>
+        <v>-151.044</v>
       </c>
       <c r="F13">
-        <v>39.743</v>
+        <v>43.356</v>
       </c>
       <c r="G13">
         <v>81.59999999999999</v>
@@ -2341,45 +2341,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M13">
-        <v>2.0586874</v>
+        <v>2.319546</v>
       </c>
       <c r="N13">
-        <v>19.96631259999999</v>
+        <v>19.70545399999999</v>
       </c>
       <c r="O13">
-        <v>5.151308650799998</v>
+        <v>5.084007131999998</v>
       </c>
       <c r="P13">
-        <v>14.81500394919999</v>
+        <v>14.62144686799999</v>
       </c>
       <c r="Q13">
-        <v>46.4150039492</v>
+        <v>46.22144686799999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1020981412557626</v>
+        <v>0.1025867023095109</v>
       </c>
       <c r="T13">
-        <v>1.30018801976357</v>
+        <v>1.311471184977157</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.69856453194399</v>
+        <v>9.49539263286867</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09503993803236958</v>
+        <v>0.09484586034711043</v>
       </c>
       <c r="C14">
-        <v>300.9435691473312</v>
+        <v>297.6834962605166</v>
       </c>
       <c r="D14">
-        <v>262.6995691473313</v>
+        <v>263.0524962605166</v>
       </c>
       <c r="E14">
-        <v>-151.044</v>
+        <v>-147.431</v>
       </c>
       <c r="F14">
-        <v>43.356</v>
+        <v>46.969</v>
       </c>
       <c r="G14">
         <v>81.59999999999999</v>
@@ -2423,28 +2423,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M14">
-        <v>2.319546</v>
+        <v>2.5128415</v>
       </c>
       <c r="N14">
-        <v>19.70545399999999</v>
+        <v>19.51215849999999</v>
       </c>
       <c r="O14">
-        <v>5.084007131999998</v>
+        <v>5.034136892999998</v>
       </c>
       <c r="P14">
-        <v>14.62144686799999</v>
+        <v>14.47802160699999</v>
       </c>
       <c r="Q14">
-        <v>46.22144686799999</v>
+        <v>46.078021607</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1025867023095109</v>
+        <v>0.1030864946518511</v>
       </c>
       <c r="T14">
-        <v>1.311471184977157</v>
+        <v>1.323013733299101</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.49539263286867</v>
+        <v>8.764977814955696</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09484586034711043</v>
+        <v>0.09465178266185131</v>
       </c>
       <c r="C15">
-        <v>297.6834962605166</v>
+        <v>294.4243729383409</v>
       </c>
       <c r="D15">
-        <v>263.0524962605166</v>
+        <v>263.4063729383409</v>
       </c>
       <c r="E15">
-        <v>-147.431</v>
+        <v>-143.818</v>
       </c>
       <c r="F15">
-        <v>46.969</v>
+        <v>50.58200000000001</v>
       </c>
       <c r="G15">
         <v>81.59999999999999</v>
@@ -2505,28 +2505,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M15">
-        <v>2.5128415</v>
+        <v>2.706137</v>
       </c>
       <c r="N15">
-        <v>19.51215849999999</v>
+        <v>19.31886299999999</v>
       </c>
       <c r="O15">
-        <v>5.034136892999998</v>
+        <v>4.984266653999997</v>
       </c>
       <c r="P15">
-        <v>14.47802160699999</v>
+        <v>14.33459634599999</v>
       </c>
       <c r="Q15">
-        <v>46.078021607</v>
+        <v>45.93459634599999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1030864946518511</v>
+        <v>0.1035979100719201</v>
       </c>
       <c r="T15">
-        <v>1.323013733299101</v>
+        <v>1.33482471297737</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.764977814955696</v>
+        <v>8.138907971030285</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09465178266185131</v>
+        <v>0.09454674497659217</v>
       </c>
       <c r="C16">
-        <v>294.4243729383409</v>
+        <v>291.0032935624648</v>
       </c>
       <c r="D16">
-        <v>263.4063729383409</v>
+        <v>263.5982935624648</v>
       </c>
       <c r="E16">
-        <v>-143.818</v>
+        <v>-140.205</v>
       </c>
       <c r="F16">
-        <v>50.58200000000001</v>
+        <v>54.19500000000001</v>
       </c>
       <c r="G16">
         <v>81.59999999999999</v>
@@ -2587,45 +2587,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M16">
-        <v>2.706137</v>
+        <v>2.9427885</v>
       </c>
       <c r="N16">
-        <v>19.31886299999999</v>
+        <v>19.08221149999999</v>
       </c>
       <c r="O16">
-        <v>4.984266653999997</v>
+        <v>4.923210566999998</v>
       </c>
       <c r="P16">
-        <v>14.33459634599999</v>
+        <v>14.15900093299999</v>
       </c>
       <c r="Q16">
-        <v>45.93459634599999</v>
+        <v>45.759000933</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1035979100719201</v>
+        <v>0.1041213587959908</v>
       </c>
       <c r="T16">
-        <v>1.33482471297737</v>
+        <v>1.346913598059834</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.138907971030285</v>
+        <v>7.484397876367939</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09454674497659217</v>
+        <v>0.09435860329133303</v>
       </c>
       <c r="C17">
-        <v>291.0032935624648</v>
+        <v>287.7347584882457</v>
       </c>
       <c r="D17">
-        <v>263.5982935624648</v>
+        <v>263.9427584882457</v>
       </c>
       <c r="E17">
-        <v>-140.205</v>
+        <v>-136.592</v>
       </c>
       <c r="F17">
-        <v>54.195</v>
+        <v>57.808</v>
       </c>
       <c r="G17">
         <v>81.59999999999999</v>
@@ -2669,28 +2669,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M17">
-        <v>2.9427885</v>
+        <v>3.1389744</v>
       </c>
       <c r="N17">
-        <v>19.08221149999999</v>
+        <v>18.88602559999999</v>
       </c>
       <c r="O17">
-        <v>4.923210566999998</v>
+        <v>4.872594604799998</v>
       </c>
       <c r="P17">
-        <v>14.15900093299999</v>
+        <v>14.01343099519999</v>
       </c>
       <c r="Q17">
-        <v>45.759000933</v>
+        <v>45.6134309952</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1041213587959908</v>
+        <v>0.1046572705849203</v>
       </c>
       <c r="T17">
-        <v>1.346913598059834</v>
+        <v>1.359290313739498</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.484397876367939</v>
+        <v>7.016623009094943</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09435860329133303</v>
+        <v>0.0941704616060739</v>
       </c>
       <c r="C18">
-        <v>287.7347584882457</v>
+        <v>284.4671248716481</v>
       </c>
       <c r="D18">
-        <v>263.9427584882457</v>
+        <v>264.2881248716481</v>
       </c>
       <c r="E18">
-        <v>-136.592</v>
+        <v>-132.979</v>
       </c>
       <c r="F18">
-        <v>57.808</v>
+        <v>61.42100000000001</v>
       </c>
       <c r="G18">
         <v>81.59999999999999</v>
@@ -2751,28 +2751,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M18">
-        <v>3.1389744</v>
+        <v>3.335160300000001</v>
       </c>
       <c r="N18">
-        <v>18.88602559999999</v>
+        <v>18.68983969999999</v>
       </c>
       <c r="O18">
-        <v>4.872594604799998</v>
+        <v>4.821978642599998</v>
       </c>
       <c r="P18">
-        <v>14.01343099519999</v>
+        <v>13.86786105739999</v>
       </c>
       <c r="Q18">
-        <v>45.6134309952</v>
+        <v>45.46786105739999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1046572705849203</v>
+        <v>0.1052060959109324</v>
       </c>
       <c r="T18">
-        <v>1.359290313739498</v>
+        <v>1.371965263531926</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.016623009094943</v>
+        <v>6.60388047914818</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0941704616060739</v>
+        <v>0.09398231992081474</v>
       </c>
       <c r="C19">
-        <v>284.4671248716481</v>
+        <v>281.2003962559522</v>
       </c>
       <c r="D19">
-        <v>264.2881248716481</v>
+        <v>264.6343962559523</v>
       </c>
       <c r="E19">
-        <v>-132.979</v>
+        <v>-129.366</v>
       </c>
       <c r="F19">
-        <v>61.42100000000001</v>
+        <v>65.03400000000001</v>
       </c>
       <c r="G19">
         <v>81.59999999999999</v>
@@ -2833,28 +2833,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M19">
-        <v>3.335160300000001</v>
+        <v>3.5313462</v>
       </c>
       <c r="N19">
-        <v>18.68983969999999</v>
+        <v>18.49365379999999</v>
       </c>
       <c r="O19">
-        <v>4.821978642599998</v>
+        <v>4.771362680399998</v>
       </c>
       <c r="P19">
-        <v>13.86786105739999</v>
+        <v>13.72229111959999</v>
       </c>
       <c r="Q19">
-        <v>45.46786105739999</v>
+        <v>45.3222911196</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1052060959109324</v>
+        <v>0.1057683072205058</v>
       </c>
       <c r="T19">
-        <v>1.371965263531926</v>
+        <v>1.384949358441243</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.60388047914818</v>
+        <v>6.236998230306614</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09398231992081475</v>
+        <v>0.09393515823555564</v>
       </c>
       <c r="C20">
-        <v>281.2003962559522</v>
+        <v>277.674338769122</v>
       </c>
       <c r="D20">
-        <v>264.6343962559522</v>
+        <v>264.721338769122</v>
       </c>
       <c r="E20">
-        <v>-129.366</v>
+        <v>-125.753</v>
       </c>
       <c r="F20">
-        <v>65.03400000000001</v>
+        <v>68.64700000000001</v>
       </c>
       <c r="G20">
         <v>81.59999999999999</v>
@@ -2915,45 +2915,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M20">
-        <v>3.5313462</v>
+        <v>3.7961791</v>
       </c>
       <c r="N20">
-        <v>18.49365379999999</v>
+        <v>18.22882089999999</v>
       </c>
       <c r="O20">
-        <v>4.771362680399998</v>
+        <v>4.703035792199998</v>
       </c>
       <c r="P20">
-        <v>13.72229111959999</v>
+        <v>13.52578510779999</v>
       </c>
       <c r="Q20">
-        <v>45.3222911196</v>
+        <v>45.1257851078</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1057683072205058</v>
+        <v>0.1063444002908094</v>
       </c>
       <c r="T20">
-        <v>1.384949358441243</v>
+        <v>1.398254048286592</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.236998230306614</v>
+        <v>5.801886428382684</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09393515823555564</v>
+        <v>0.09375443655029647</v>
       </c>
       <c r="C21">
-        <v>277.674338769122</v>
+        <v>274.3950285435126</v>
       </c>
       <c r="D21">
-        <v>264.721338769122</v>
+        <v>265.0550285435126</v>
       </c>
       <c r="E21">
-        <v>-125.753</v>
+        <v>-122.14</v>
       </c>
       <c r="F21">
-        <v>68.64700000000001</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="G21">
         <v>81.59999999999999</v>
@@ -2997,28 +2997,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M21">
-        <v>3.7961791</v>
+        <v>3.995978</v>
       </c>
       <c r="N21">
-        <v>18.22882089999999</v>
+        <v>18.02902199999999</v>
       </c>
       <c r="O21">
-        <v>4.703035792199998</v>
+        <v>4.651487675999998</v>
       </c>
       <c r="P21">
-        <v>13.52578510779999</v>
+        <v>13.37753432399999</v>
       </c>
       <c r="Q21">
-        <v>45.1257851078</v>
+        <v>44.97753432399999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1063444002908094</v>
+        <v>0.1069348956878706</v>
       </c>
       <c r="T21">
-        <v>1.398254048286592</v>
+        <v>1.411891355378074</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.801886428382684</v>
+        <v>5.511792106963549</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09375443655029647</v>
+        <v>0.09357371486503735</v>
       </c>
       <c r="C22">
-        <v>274.3950285435126</v>
+        <v>271.1165606330865</v>
       </c>
       <c r="D22">
-        <v>265.0550285435126</v>
+        <v>265.3895606330865</v>
       </c>
       <c r="E22">
-        <v>-122.14</v>
+        <v>-118.527</v>
       </c>
       <c r="F22">
-        <v>72.26000000000001</v>
+        <v>75.873</v>
       </c>
       <c r="G22">
         <v>81.59999999999999</v>
@@ -3079,28 +3079,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M22">
-        <v>3.995978</v>
+        <v>4.1957769</v>
       </c>
       <c r="N22">
-        <v>18.02902199999999</v>
+        <v>17.82922309999999</v>
       </c>
       <c r="O22">
-        <v>4.651487675999998</v>
+        <v>4.599939559799998</v>
       </c>
       <c r="P22">
-        <v>13.37753432399999</v>
+        <v>13.22928354019999</v>
       </c>
       <c r="Q22">
-        <v>44.97753432399999</v>
+        <v>44.8292835402</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1069348956878706</v>
+        <v>0.1075403403354903</v>
       </c>
       <c r="T22">
-        <v>1.411891355378074</v>
+        <v>1.425873910750354</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.511792106963549</v>
+        <v>5.249325816155761</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09357371486503735</v>
+        <v>0.0933929931797782</v>
       </c>
       <c r="C23">
-        <v>271.1165606330865</v>
+        <v>267.8389382311908</v>
       </c>
       <c r="D23">
-        <v>265.3895606330865</v>
+        <v>265.7249382311908</v>
       </c>
       <c r="E23">
-        <v>-118.527</v>
+        <v>-114.914</v>
       </c>
       <c r="F23">
-        <v>75.873</v>
+        <v>79.486</v>
       </c>
       <c r="G23">
         <v>81.59999999999999</v>
@@ -3161,28 +3161,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M23">
-        <v>4.1957769</v>
+        <v>4.3955758</v>
       </c>
       <c r="N23">
-        <v>17.82922309999999</v>
+        <v>17.62942419999999</v>
       </c>
       <c r="O23">
-        <v>4.599939559799998</v>
+        <v>4.548391443599998</v>
       </c>
       <c r="P23">
-        <v>13.22928354019999</v>
+        <v>13.08103275639999</v>
       </c>
       <c r="Q23">
-        <v>44.8292835402</v>
+        <v>44.68103275639999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1075403403354903</v>
+        <v>0.1081613092048438</v>
       </c>
       <c r="T23">
-        <v>1.425873910750354</v>
+        <v>1.440214993183461</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.249325816155761</v>
+        <v>5.010720097239591</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0933929931797782</v>
+        <v>0.09321227149451906</v>
       </c>
       <c r="C24">
-        <v>267.8389382311908</v>
+        <v>264.5621645473347</v>
       </c>
       <c r="D24">
-        <v>265.7249382311908</v>
+        <v>266.0611645473347</v>
       </c>
       <c r="E24">
-        <v>-114.914</v>
+        <v>-111.301</v>
       </c>
       <c r="F24">
-        <v>79.486</v>
+        <v>83.099</v>
       </c>
       <c r="G24">
         <v>81.59999999999999</v>
@@ -3243,28 +3243,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M24">
-        <v>4.3955758</v>
+        <v>4.595374700000001</v>
       </c>
       <c r="N24">
-        <v>17.62942419999999</v>
+        <v>17.42962529999999</v>
       </c>
       <c r="O24">
-        <v>4.548391443599998</v>
+        <v>4.496843327399998</v>
       </c>
       <c r="P24">
-        <v>13.08103275639999</v>
+        <v>12.93278197259999</v>
       </c>
       <c r="Q24">
-        <v>44.68103275639999</v>
+        <v>44.53278197259999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1081613092048438</v>
+        <v>0.108798407135739</v>
       </c>
       <c r="T24">
-        <v>1.440214993183461</v>
+        <v>1.454928571264182</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.010720097239591</v>
+        <v>4.792862701707434</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09321227149451906</v>
+        <v>0.09303154980925994</v>
       </c>
       <c r="C25">
-        <v>264.5621645473347</v>
+        <v>261.2862428072923</v>
       </c>
       <c r="D25">
-        <v>266.0611645473347</v>
+        <v>266.3982428072923</v>
       </c>
       <c r="E25">
-        <v>-111.301</v>
+        <v>-107.688</v>
       </c>
       <c r="F25">
-        <v>83.099</v>
+        <v>86.712</v>
       </c>
       <c r="G25">
         <v>81.59999999999999</v>
@@ -3325,28 +3325,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M25">
-        <v>4.595374700000001</v>
+        <v>4.7951736</v>
       </c>
       <c r="N25">
-        <v>17.42962529999999</v>
+        <v>17.22982639999999</v>
       </c>
       <c r="O25">
-        <v>4.496843327399998</v>
+        <v>4.445295211199999</v>
       </c>
       <c r="P25">
-        <v>12.93278197259999</v>
+        <v>12.7845311888</v>
       </c>
       <c r="Q25">
-        <v>44.53278197259999</v>
+        <v>44.3845311888</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.108798407135739</v>
+        <v>0.1094522708016578</v>
       </c>
       <c r="T25">
-        <v>1.454928571264182</v>
+        <v>1.470029348768079</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.792862701707434</v>
+        <v>4.593160089136292</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09303154980925994</v>
+        <v>0.09331457812400082</v>
       </c>
       <c r="C26">
-        <v>261.2862428072923</v>
+        <v>257.1457222498991</v>
       </c>
       <c r="D26">
-        <v>266.3982428072923</v>
+        <v>265.8707222498991</v>
       </c>
       <c r="E26">
-        <v>-107.688</v>
+        <v>-104.075</v>
       </c>
       <c r="F26">
-        <v>86.712</v>
+        <v>90.325</v>
       </c>
       <c r="G26">
         <v>81.59999999999999</v>
@@ -3407,45 +3407,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M26">
-        <v>4.7951736</v>
+        <v>5.220785</v>
       </c>
       <c r="N26">
-        <v>17.22982639999999</v>
+        <v>16.80421499999999</v>
       </c>
       <c r="O26">
-        <v>4.445295211199999</v>
+        <v>4.335487469999998</v>
       </c>
       <c r="P26">
-        <v>12.7845311888</v>
+        <v>12.46872753</v>
       </c>
       <c r="Q26">
-        <v>44.3845311888</v>
+        <v>44.06872753</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1094522708016578</v>
+        <v>0.1101235708320011</v>
       </c>
       <c r="T26">
-        <v>1.470029348768079</v>
+        <v>1.48553281367208</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.593160089136292</v>
+        <v>4.218714235502897</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09331457812400082</v>
+        <v>0.09315240643874166</v>
       </c>
       <c r="C27">
-        <v>257.1457222498991</v>
+        <v>253.8347290589545</v>
       </c>
       <c r="D27">
-        <v>265.8707222498991</v>
+        <v>266.1727290589545</v>
       </c>
       <c r="E27">
-        <v>-104.075</v>
+        <v>-100.462</v>
       </c>
       <c r="F27">
-        <v>90.325</v>
+        <v>93.938</v>
       </c>
       <c r="G27">
         <v>81.59999999999999</v>
@@ -3489,28 +3489,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M27">
-        <v>5.220785</v>
+        <v>5.4296164</v>
       </c>
       <c r="N27">
-        <v>16.80421499999999</v>
+        <v>16.59538359999999</v>
       </c>
       <c r="O27">
-        <v>4.335487469999998</v>
+        <v>4.281608968799998</v>
       </c>
       <c r="P27">
-        <v>12.46872753</v>
+        <v>12.31377463119999</v>
       </c>
       <c r="Q27">
-        <v>44.06872753</v>
+        <v>43.9137746312</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1101235708320011</v>
+        <v>0.1108130141064076</v>
       </c>
       <c r="T27">
-        <v>1.48553281367208</v>
+        <v>1.501455291141055</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.218714235502897</v>
+        <v>4.056455995675861</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09315240643874166</v>
+        <v>0.09369142475348254</v>
       </c>
       <c r="C28">
-        <v>253.8347290589545</v>
+        <v>249.2205732383891</v>
       </c>
       <c r="D28">
-        <v>266.1727290589545</v>
+        <v>265.1715732383891</v>
       </c>
       <c r="E28">
-        <v>-100.462</v>
+        <v>-96.84899999999999</v>
       </c>
       <c r="F28">
-        <v>93.938</v>
+        <v>97.55100000000002</v>
       </c>
       <c r="G28">
         <v>81.59999999999999</v>
@@ -3571,45 +3571,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M28">
-        <v>5.4296164</v>
+        <v>5.979876300000001</v>
       </c>
       <c r="N28">
-        <v>16.59538359999999</v>
+        <v>16.04512369999999</v>
       </c>
       <c r="O28">
-        <v>4.281608968799998</v>
+        <v>4.139641914599998</v>
       </c>
       <c r="P28">
-        <v>12.31377463119999</v>
+        <v>11.90548178539999</v>
       </c>
       <c r="Q28">
-        <v>43.9137746312</v>
+        <v>43.50548178539999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1108130141064076</v>
+        <v>0.1115213462376473</v>
       </c>
       <c r="T28">
-        <v>1.501455291141055</v>
+        <v>1.517814000869453</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.056455995675861</v>
+        <v>3.683186556885798</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09369142475348254</v>
+        <v>0.09355522306822339</v>
       </c>
       <c r="C29">
-        <v>249.2205732383891</v>
+        <v>245.8598382408961</v>
       </c>
       <c r="D29">
-        <v>265.1715732383891</v>
+        <v>265.4238382408961</v>
       </c>
       <c r="E29">
-        <v>-96.84899999999999</v>
+        <v>-93.23599999999999</v>
       </c>
       <c r="F29">
-        <v>97.55100000000002</v>
+        <v>101.164</v>
       </c>
       <c r="G29">
         <v>81.59999999999999</v>
@@ -3653,28 +3653,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M29">
-        <v>5.979876300000001</v>
+        <v>6.201353200000001</v>
       </c>
       <c r="N29">
-        <v>16.04512369999999</v>
+        <v>15.82364679999999</v>
       </c>
       <c r="O29">
-        <v>4.139641914599998</v>
+        <v>4.082500874399998</v>
       </c>
       <c r="P29">
-        <v>11.90548178539999</v>
+        <v>11.74114592559999</v>
       </c>
       <c r="Q29">
-        <v>43.50548178539999</v>
+        <v>43.3411459256</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1115213462376473</v>
+        <v>0.1122493542614214</v>
       </c>
       <c r="T29">
-        <v>1.517814000869453</v>
+        <v>1.534627119201418</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.683186556885798</v>
+        <v>3.551644179854163</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09355522306822339</v>
+        <v>0.09402152538296425</v>
       </c>
       <c r="C30">
-        <v>245.8598382408961</v>
+        <v>241.3851644894078</v>
       </c>
       <c r="D30">
-        <v>265.4238382408961</v>
+        <v>264.5621644894078</v>
       </c>
       <c r="E30">
-        <v>-93.23599999999999</v>
+        <v>-89.62299999999999</v>
       </c>
       <c r="F30">
-        <v>101.164</v>
+        <v>104.777</v>
       </c>
       <c r="G30">
         <v>81.59999999999999</v>
@@ -3735,45 +3735,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M30">
-        <v>6.201353200000001</v>
+        <v>6.716205700000001</v>
       </c>
       <c r="N30">
-        <v>15.82364679999999</v>
+        <v>15.30879429999999</v>
       </c>
       <c r="O30">
-        <v>4.082500874399998</v>
+        <v>3.949668929399997</v>
       </c>
       <c r="P30">
-        <v>11.74114592559999</v>
+        <v>11.35912537059999</v>
       </c>
       <c r="Q30">
-        <v>43.3411459256</v>
+        <v>42.95912537059999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1122493542614214</v>
+        <v>0.1129978695534708</v>
       </c>
       <c r="T30">
-        <v>1.534627119201418</v>
+        <v>1.55191384650048</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.551644179854163</v>
+        <v>3.279381392383498</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09402152538296424</v>
+        <v>0.09390609969770512</v>
       </c>
       <c r="C31">
-        <v>241.3851644894078</v>
+        <v>237.9849365999055</v>
       </c>
       <c r="D31">
-        <v>264.5621644894078</v>
+        <v>264.7749365999055</v>
       </c>
       <c r="E31">
-        <v>-89.623</v>
+        <v>-86.01000000000001</v>
       </c>
       <c r="F31">
-        <v>104.777</v>
+        <v>108.39</v>
       </c>
       <c r="G31">
         <v>81.59999999999999</v>
@@ -3817,28 +3817,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M31">
-        <v>6.716205700000001</v>
+        <v>6.947799000000001</v>
       </c>
       <c r="N31">
-        <v>15.30879429999999</v>
+        <v>15.07720099999999</v>
       </c>
       <c r="O31">
-        <v>3.949668929399998</v>
+        <v>3.889917857999998</v>
       </c>
       <c r="P31">
-        <v>11.35912537059999</v>
+        <v>11.18728314199999</v>
       </c>
       <c r="Q31">
-        <v>42.95912537059999</v>
+        <v>42.78728314199999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1129978695534708</v>
+        <v>0.1137677709967216</v>
       </c>
       <c r="T31">
-        <v>1.55191384650048</v>
+        <v>1.569694480293802</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.279381392383498</v>
+        <v>3.170068679304049</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09390609969770512</v>
+        <v>0.09379067401244598</v>
       </c>
       <c r="C32">
-        <v>237.9849365999055</v>
+        <v>234.5850512265754</v>
       </c>
       <c r="D32">
-        <v>264.7749365999055</v>
+        <v>264.9880512265755</v>
       </c>
       <c r="E32">
-        <v>-86.01000000000001</v>
+        <v>-82.39700000000001</v>
       </c>
       <c r="F32">
-        <v>108.39</v>
+        <v>112.003</v>
       </c>
       <c r="G32">
         <v>81.59999999999999</v>
@@ -3899,28 +3899,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M32">
-        <v>6.947799000000001</v>
+        <v>7.179392300000001</v>
       </c>
       <c r="N32">
-        <v>15.07720099999999</v>
+        <v>14.84560769999999</v>
       </c>
       <c r="O32">
-        <v>3.889917857999998</v>
+        <v>3.830166786599998</v>
       </c>
       <c r="P32">
-        <v>11.18728314199999</v>
+        <v>11.01544091339999</v>
       </c>
       <c r="Q32">
-        <v>42.78728314199999</v>
+        <v>42.61544091339999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1137677709967216</v>
+        <v>0.1145599884238348</v>
       </c>
       <c r="T32">
-        <v>1.569694480293802</v>
+        <v>1.587990494776785</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.170068679304049</v>
+        <v>3.067808399326499</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09379067401244598</v>
+        <v>0.09552728032718685</v>
       </c>
       <c r="C33">
-        <v>234.5850512265754</v>
+        <v>227.8015057964925</v>
       </c>
       <c r="D33">
-        <v>264.9880512265755</v>
+        <v>261.8175057964925</v>
       </c>
       <c r="E33">
-        <v>-82.39700000000001</v>
+        <v>-78.78400000000001</v>
       </c>
       <c r="F33">
-        <v>112.003</v>
+        <v>115.616</v>
       </c>
       <c r="G33">
         <v>81.59999999999999</v>
@@ -3981,45 +3981,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M33">
-        <v>7.179392300000001</v>
+        <v>8.312790400000001</v>
       </c>
       <c r="N33">
-        <v>14.84560769999999</v>
+        <v>13.71220959999999</v>
       </c>
       <c r="O33">
-        <v>3.830166786599998</v>
+        <v>3.537750076799998</v>
       </c>
       <c r="P33">
-        <v>11.01544091339999</v>
+        <v>10.17445952319999</v>
       </c>
       <c r="Q33">
-        <v>42.61544091339999</v>
+        <v>41.77445952319999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1145599884238348</v>
+        <v>0.1153755063635101</v>
       </c>
       <c r="T33">
-        <v>1.587990494776785</v>
+        <v>1.606824627332796</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.067808399326499</v>
+        <v>2.649531497871038</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09552728032718685</v>
+        <v>0.09546973064192771</v>
       </c>
       <c r="C34">
-        <v>227.8015057964925</v>
+        <v>224.2923590679433</v>
       </c>
       <c r="D34">
-        <v>261.8175057964925</v>
+        <v>261.9213590679433</v>
       </c>
       <c r="E34">
-        <v>-78.78400000000001</v>
+        <v>-75.17099999999999</v>
       </c>
       <c r="F34">
-        <v>115.616</v>
+        <v>119.229</v>
       </c>
       <c r="G34">
         <v>81.59999999999999</v>
@@ -4063,28 +4063,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M34">
-        <v>8.312790400000001</v>
+        <v>8.572565100000002</v>
       </c>
       <c r="N34">
-        <v>13.71220959999999</v>
+        <v>13.45243489999999</v>
       </c>
       <c r="O34">
-        <v>3.537750076799998</v>
+        <v>3.470728204199997</v>
       </c>
       <c r="P34">
-        <v>10.17445952319999</v>
+        <v>9.981706695799993</v>
       </c>
       <c r="Q34">
-        <v>41.77445952319999</v>
+        <v>41.58170669579999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1153755063635101</v>
+        <v>0.1162153681222802</v>
       </c>
       <c r="T34">
-        <v>1.606824627332796</v>
+        <v>1.626220972800928</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.649531497871038</v>
+        <v>2.569242664602219</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09546973064192771</v>
+        <v>0.09639607295666855</v>
       </c>
       <c r="C35">
-        <v>224.2923590679433</v>
+        <v>219.0176427685953</v>
       </c>
       <c r="D35">
-        <v>261.9213590679433</v>
+        <v>260.2596427685954</v>
       </c>
       <c r="E35">
-        <v>-75.17099999999999</v>
+        <v>-71.55799999999999</v>
       </c>
       <c r="F35">
-        <v>119.229</v>
+        <v>122.842</v>
       </c>
       <c r="G35">
         <v>81.59999999999999</v>
@@ -4145,45 +4145,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M35">
-        <v>8.572565100000002</v>
+        <v>9.311423600000001</v>
       </c>
       <c r="N35">
-        <v>13.45243489999999</v>
+        <v>12.71357639999999</v>
       </c>
       <c r="O35">
-        <v>3.470728204199997</v>
+        <v>3.280102711199997</v>
       </c>
       <c r="P35">
-        <v>9.981706695799993</v>
+        <v>9.433473688799992</v>
       </c>
       <c r="Q35">
-        <v>41.58170669579999</v>
+        <v>41.03347368879999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1162153681222802</v>
+        <v>0.1170806802373766</v>
       </c>
       <c r="T35">
-        <v>1.626220972800928</v>
+        <v>1.646205086313548</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.569242664602219</v>
+        <v>2.36537407663421</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09639607295666855</v>
+        <v>0.09636746127140944</v>
       </c>
       <c r="C36">
-        <v>219.0176427685953</v>
+        <v>215.4556521245949</v>
       </c>
       <c r="D36">
-        <v>260.2596427685954</v>
+        <v>260.3106521245949</v>
       </c>
       <c r="E36">
-        <v>-71.55799999999999</v>
+        <v>-67.94499999999999</v>
       </c>
       <c r="F36">
-        <v>122.842</v>
+        <v>126.455</v>
       </c>
       <c r="G36">
         <v>81.59999999999999</v>
@@ -4227,28 +4227,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M36">
-        <v>9.311423600000001</v>
+        <v>9.585289000000001</v>
       </c>
       <c r="N36">
-        <v>12.71357639999999</v>
+        <v>12.43971099999999</v>
       </c>
       <c r="O36">
-        <v>3.280102711199997</v>
+        <v>3.209445437999998</v>
       </c>
       <c r="P36">
-        <v>9.433473688799992</v>
+        <v>9.230265561999992</v>
       </c>
       <c r="Q36">
-        <v>41.03347368879999</v>
+        <v>40.83026556199999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1170806802373766</v>
+        <v>0.1179726173406299</v>
       </c>
       <c r="T36">
-        <v>1.646205086313548</v>
+        <v>1.666804095626557</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.36537407663421</v>
+        <v>2.297791960158946</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09636746127140944</v>
+        <v>0.0963388495861503</v>
       </c>
       <c r="C37">
-        <v>215.4556521245949</v>
+        <v>211.8936814795804</v>
       </c>
       <c r="D37">
-        <v>260.3106521245949</v>
+        <v>260.3616814795804</v>
       </c>
       <c r="E37">
-        <v>-67.94499999999999</v>
+        <v>-64.33199999999999</v>
       </c>
       <c r="F37">
-        <v>126.455</v>
+        <v>130.068</v>
       </c>
       <c r="G37">
         <v>81.59999999999999</v>
@@ -4309,28 +4309,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M37">
-        <v>9.585289000000001</v>
+        <v>9.859154400000001</v>
       </c>
       <c r="N37">
-        <v>12.43971099999999</v>
+        <v>12.16584559999999</v>
       </c>
       <c r="O37">
-        <v>3.209445437999998</v>
+        <v>3.138788164799998</v>
       </c>
       <c r="P37">
-        <v>9.230265561999992</v>
+        <v>9.027057435199993</v>
       </c>
       <c r="Q37">
-        <v>40.83026556199999</v>
+        <v>40.62705743519999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1179726173406299</v>
+        <v>0.1188924274783598</v>
       </c>
       <c r="T37">
-        <v>1.666804095626557</v>
+        <v>1.688046823980597</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.297791960158946</v>
+        <v>2.233964405710087</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0963388495861503</v>
+        <v>0.09631023790089116</v>
       </c>
       <c r="C38">
-        <v>211.8936814795804</v>
+        <v>208.3317308453155</v>
       </c>
       <c r="D38">
-        <v>260.3616814795804</v>
+        <v>260.4127308453155</v>
       </c>
       <c r="E38">
-        <v>-64.33199999999999</v>
+        <v>-60.71899999999999</v>
       </c>
       <c r="F38">
-        <v>130.068</v>
+        <v>133.681</v>
       </c>
       <c r="G38">
         <v>81.59999999999999</v>
@@ -4391,28 +4391,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M38">
-        <v>9.859154400000001</v>
+        <v>10.1330198</v>
       </c>
       <c r="N38">
-        <v>12.16584559999999</v>
+        <v>11.89198019999999</v>
       </c>
       <c r="O38">
-        <v>3.138788164799998</v>
+        <v>3.068130891599997</v>
       </c>
       <c r="P38">
-        <v>9.027057435199993</v>
+        <v>8.823849308399993</v>
       </c>
       <c r="Q38">
-        <v>40.62705743519999</v>
+        <v>40.42384930839999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1188924274783598</v>
+        <v>0.1198414379379225</v>
       </c>
       <c r="T38">
-        <v>1.688046823980597</v>
+        <v>1.709963924663337</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.233964405710087</v>
+        <v>2.173586989339544</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09631023790089116</v>
+        <v>0.09628162621563202</v>
       </c>
       <c r="C39">
-        <v>208.3317308453155</v>
+        <v>204.7698002335731</v>
       </c>
       <c r="D39">
-        <v>260.4127308453155</v>
+        <v>260.4638002335731</v>
       </c>
       <c r="E39">
-        <v>-60.71899999999999</v>
+        <v>-57.10599999999999</v>
       </c>
       <c r="F39">
-        <v>133.681</v>
+        <v>137.294</v>
       </c>
       <c r="G39">
         <v>81.59999999999999</v>
@@ -4473,28 +4473,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M39">
-        <v>10.1330198</v>
+        <v>10.4068852</v>
       </c>
       <c r="N39">
-        <v>11.89198019999999</v>
+        <v>11.61811479999999</v>
       </c>
       <c r="O39">
-        <v>3.068130891599997</v>
+        <v>2.997473618399998</v>
       </c>
       <c r="P39">
-        <v>8.823849308399993</v>
+        <v>8.620641181599993</v>
       </c>
       <c r="Q39">
-        <v>40.42384930839999</v>
+        <v>40.22064118159999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1198414379379225</v>
+        <v>0.1208210616381162</v>
       </c>
       <c r="T39">
-        <v>1.709963924663337</v>
+        <v>1.732588028593907</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.173586989339544</v>
+        <v>2.116387331725345</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09628162621563202</v>
+        <v>0.09625301453037288</v>
       </c>
       <c r="C40">
-        <v>204.7698002335731</v>
+        <v>201.2078896561353</v>
       </c>
       <c r="D40">
-        <v>260.4638002335731</v>
+        <v>260.5148896561353</v>
       </c>
       <c r="E40">
-        <v>-57.10599999999999</v>
+        <v>-53.49299999999999</v>
       </c>
       <c r="F40">
-        <v>137.294</v>
+        <v>140.907</v>
       </c>
       <c r="G40">
         <v>81.59999999999999</v>
@@ -4555,28 +4555,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M40">
-        <v>10.4068852</v>
+        <v>10.6807506</v>
       </c>
       <c r="N40">
-        <v>11.61811479999999</v>
+        <v>11.34424939999999</v>
       </c>
       <c r="O40">
-        <v>2.997473618399998</v>
+        <v>2.926816345199998</v>
       </c>
       <c r="P40">
-        <v>8.620641181599993</v>
+        <v>8.417433054799993</v>
       </c>
       <c r="Q40">
-        <v>40.22064118159999</v>
+        <v>40.01743305479999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1208210616381162</v>
+        <v>0.1218328041481523</v>
       </c>
       <c r="T40">
-        <v>1.732588028593907</v>
+        <v>1.755953906423841</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.116387331725345</v>
+        <v>2.062120989886234</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09625301453037288</v>
+        <v>0.09622440284511376</v>
       </c>
       <c r="C41">
-        <v>201.2078896561353</v>
+        <v>197.6459991247935</v>
       </c>
       <c r="D41">
-        <v>260.5148896561353</v>
+        <v>260.5659991247935</v>
       </c>
       <c r="E41">
-        <v>-53.49299999999999</v>
+        <v>-49.88</v>
       </c>
       <c r="F41">
-        <v>140.907</v>
+        <v>144.52</v>
       </c>
       <c r="G41">
         <v>81.59999999999999</v>
@@ -4637,28 +4637,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M41">
-        <v>10.6807506</v>
+        <v>10.954616</v>
       </c>
       <c r="N41">
-        <v>11.34424939999999</v>
+        <v>11.07038399999999</v>
       </c>
       <c r="O41">
-        <v>2.926816345199998</v>
+        <v>2.856159071999997</v>
       </c>
       <c r="P41">
-        <v>8.417433054799993</v>
+        <v>8.214224927999993</v>
       </c>
       <c r="Q41">
-        <v>40.01743305479999</v>
+        <v>39.81422492799999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1218328041481523</v>
+        <v>0.1228782714085229</v>
       </c>
       <c r="T41">
-        <v>1.755953906423841</v>
+        <v>1.780098646848105</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.062120989886234</v>
+        <v>2.010567965139078</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09622440284511376</v>
+        <v>0.1005157151598546</v>
       </c>
       <c r="C42">
-        <v>197.6459991247935</v>
+        <v>186.585018109575</v>
       </c>
       <c r="D42">
-        <v>260.5659991247935</v>
+        <v>253.118018109575</v>
       </c>
       <c r="E42">
-        <v>-49.88</v>
+        <v>-46.267</v>
       </c>
       <c r="F42">
-        <v>144.52</v>
+        <v>148.133</v>
       </c>
       <c r="G42">
         <v>81.59999999999999</v>
@@ -4719,45 +4719,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M42">
-        <v>10.954616</v>
+        <v>13.33197</v>
       </c>
       <c r="N42">
-        <v>11.07038399999999</v>
+        <v>8.693029999999991</v>
       </c>
       <c r="O42">
-        <v>2.856159071999997</v>
+        <v>2.242801739999998</v>
       </c>
       <c r="P42">
-        <v>8.214224927999993</v>
+        <v>6.450228259999994</v>
       </c>
       <c r="Q42">
-        <v>39.81422492799999</v>
+        <v>38.05022826</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1228782714085229</v>
+        <v>0.1239591782370417</v>
       </c>
       <c r="T42">
-        <v>1.780098646848105</v>
+        <v>1.805061853049463</v>
       </c>
       <c r="U42">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.010567965139078</v>
+        <v>1.652043921490972</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1005157151598546</v>
+        <v>0.1005924674745955</v>
       </c>
       <c r="C43">
-        <v>186.585018109575</v>
+        <v>182.8426809657282</v>
       </c>
       <c r="D43">
-        <v>253.118018109575</v>
+        <v>252.9886809657282</v>
       </c>
       <c r="E43">
-        <v>-46.267</v>
+        <v>-42.654</v>
       </c>
       <c r="F43">
-        <v>148.133</v>
+        <v>151.746</v>
       </c>
       <c r="G43">
         <v>81.59999999999999</v>
@@ -4801,28 +4801,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M43">
-        <v>13.33197</v>
+        <v>13.65714</v>
       </c>
       <c r="N43">
-        <v>8.693029999999991</v>
+        <v>8.367859999999991</v>
       </c>
       <c r="O43">
-        <v>2.242801739999998</v>
+        <v>2.158907879999998</v>
       </c>
       <c r="P43">
-        <v>6.450228259999994</v>
+        <v>6.208952119999994</v>
       </c>
       <c r="Q43">
-        <v>38.05022826</v>
+        <v>37.80895211999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1239591782370417</v>
+        <v>0.1250773577148198</v>
       </c>
       <c r="T43">
-        <v>1.805061853049463</v>
+        <v>1.830885859464661</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.652043921490972</v>
+        <v>1.612709542407853</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1005924674745955</v>
+        <v>0.1006692197893364</v>
       </c>
       <c r="C44">
-        <v>182.8426809657281</v>
+        <v>179.1004759306393</v>
       </c>
       <c r="D44">
-        <v>252.9886809657282</v>
+        <v>252.8594759306393</v>
       </c>
       <c r="E44">
-        <v>-42.654</v>
+        <v>-39.041</v>
       </c>
       <c r="F44">
-        <v>151.746</v>
+        <v>155.359</v>
       </c>
       <c r="G44">
         <v>81.59999999999999</v>
@@ -4883,28 +4883,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M44">
-        <v>13.65714</v>
+        <v>13.98231</v>
       </c>
       <c r="N44">
-        <v>8.367859999999991</v>
+        <v>8.042689999999991</v>
       </c>
       <c r="O44">
-        <v>2.158907879999998</v>
+        <v>2.075014019999998</v>
       </c>
       <c r="P44">
-        <v>6.208952119999994</v>
+        <v>5.967675979999994</v>
       </c>
       <c r="Q44">
-        <v>37.80895211999999</v>
+        <v>37.56767598</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1250773577148198</v>
+        <v>0.1262347715602392</v>
       </c>
       <c r="T44">
-        <v>1.830885859464661</v>
+        <v>1.857615971368111</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.612709542407853</v>
+        <v>1.575204669328601</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1006692197893364</v>
+        <v>0.1007459721040772</v>
       </c>
       <c r="C45">
-        <v>179.1004759306393</v>
+        <v>175.3584028020021</v>
       </c>
       <c r="D45">
-        <v>252.8594759306393</v>
+        <v>252.7304028020021</v>
       </c>
       <c r="E45">
-        <v>-39.041</v>
+        <v>-35.428</v>
       </c>
       <c r="F45">
-        <v>155.359</v>
+        <v>158.972</v>
       </c>
       <c r="G45">
         <v>81.59999999999999</v>
@@ -4965,28 +4965,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M45">
-        <v>13.98231</v>
+        <v>14.30748</v>
       </c>
       <c r="N45">
-        <v>8.042689999999991</v>
+        <v>7.717519999999991</v>
       </c>
       <c r="O45">
-        <v>2.075014019999998</v>
+        <v>1.991120159999998</v>
       </c>
       <c r="P45">
-        <v>5.967675979999994</v>
+        <v>5.726399839999994</v>
       </c>
       <c r="Q45">
-        <v>37.56767598</v>
+        <v>37.32639983999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1262347715602392</v>
+        <v>0.1274335216144236</v>
       </c>
       <c r="T45">
-        <v>1.857615971368111</v>
+        <v>1.885300730125256</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.575204669328601</v>
+        <v>1.539404563207496</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1007459721040772</v>
+        <v>0.1008227244188181</v>
       </c>
       <c r="C46">
-        <v>175.3584028020021</v>
+        <v>171.616461377923</v>
       </c>
       <c r="D46">
-        <v>252.7304028020021</v>
+        <v>252.601461377923</v>
       </c>
       <c r="E46">
-        <v>-35.428</v>
+        <v>-31.815</v>
       </c>
       <c r="F46">
-        <v>158.972</v>
+        <v>162.585</v>
       </c>
       <c r="G46">
         <v>81.59999999999999</v>
@@ -5047,28 +5047,28 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M46">
-        <v>14.30748</v>
+        <v>14.63265</v>
       </c>
       <c r="N46">
-        <v>7.717519999999991</v>
+        <v>7.392349999999992</v>
       </c>
       <c r="O46">
-        <v>1.991120159999998</v>
+        <v>1.907226299999998</v>
       </c>
       <c r="P46">
-        <v>5.726399839999994</v>
+        <v>5.485123699999994</v>
       </c>
       <c r="Q46">
-        <v>37.32639983999999</v>
+        <v>37.0851237</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1274335216144236</v>
+        <v>0.1286758625796692</v>
       </c>
       <c r="T46">
-        <v>1.885300730125256</v>
+        <v>1.913992207382661</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.539404563207496</v>
+        <v>1.505195572913997</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1008227244188181</v>
+        <v>0.1225761206330658</v>
       </c>
       <c r="C47">
-        <v>171.616461377923</v>
+        <v>136.0915812752538</v>
       </c>
       <c r="D47">
-        <v>252.601461377923</v>
+        <v>220.6895812752538</v>
       </c>
       <c r="E47">
-        <v>-31.815</v>
+        <v>-28.202</v>
       </c>
       <c r="F47">
-        <v>162.585</v>
+        <v>166.198</v>
       </c>
       <c r="G47">
         <v>81.59999999999999</v>
@@ -5129,45 +5129,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M47">
-        <v>14.63265</v>
+        <v>24.39786640000001</v>
       </c>
       <c r="N47">
-        <v>7.392349999999992</v>
+        <v>-2.372866400000014</v>
       </c>
       <c r="O47">
-        <v>1.907226299999998</v>
+        <v>-0.6121995312000036</v>
       </c>
       <c r="P47">
-        <v>5.485123699999994</v>
+        <v>-1.76066686880001</v>
       </c>
       <c r="Q47">
-        <v>37.0851237</v>
+        <v>29.83933313119999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1286758625796692</v>
+        <v>0.1310664984711928</v>
       </c>
       <c r="T47">
-        <v>1.913992207382661</v>
+        <v>1.969203197949026</v>
       </c>
       <c r="U47">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.258</v>
+        <v>0.2329076611387624</v>
       </c>
       <c r="W47">
-        <v>0.06677999999999999</v>
+        <v>0.1126091553448297</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.505195572913997</v>
+        <v>0.9027428726308619</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1225761206330658</v>
+        <v>0.1235861206330658</v>
       </c>
       <c r="C48">
-        <v>136.0915812752538</v>
+        <v>131.1916578068944</v>
       </c>
       <c r="D48">
-        <v>220.6895812752538</v>
+        <v>219.4026578068944</v>
       </c>
       <c r="E48">
-        <v>-28.202</v>
+        <v>-24.589</v>
       </c>
       <c r="F48">
-        <v>166.198</v>
+        <v>169.811</v>
       </c>
       <c r="G48">
         <v>81.59999999999999</v>
@@ -5211,37 +5211,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M48">
-        <v>24.39786640000001</v>
+        <v>24.9282548</v>
       </c>
       <c r="N48">
-        <v>-2.372866400000014</v>
+        <v>-2.903254800000013</v>
       </c>
       <c r="O48">
-        <v>-0.6121995312000036</v>
+        <v>-0.7490397384000035</v>
       </c>
       <c r="P48">
-        <v>-1.76066686880001</v>
+        <v>-2.15421506160001</v>
       </c>
       <c r="Q48">
-        <v>29.83933313119999</v>
+        <v>29.44578493839999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1310664984711928</v>
+        <v>0.1326753003291398</v>
       </c>
       <c r="T48">
-        <v>1.969203197949026</v>
+        <v>2.006357975268819</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2329076611387624</v>
+        <v>0.2279521789868738</v>
       </c>
       <c r="W48">
-        <v>0.1126091553448297</v>
+        <v>0.1133366201247269</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9027428726308619</v>
+        <v>0.8835355774685032</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1235861206330658</v>
+        <v>0.1245961206330658</v>
       </c>
       <c r="C49">
-        <v>131.1916578068944</v>
+        <v>126.3066563863916</v>
       </c>
       <c r="D49">
-        <v>219.4026578068944</v>
+        <v>218.1306563863916</v>
       </c>
       <c r="E49">
-        <v>-24.589</v>
+        <v>-20.976</v>
       </c>
       <c r="F49">
-        <v>169.811</v>
+        <v>173.424</v>
       </c>
       <c r="G49">
         <v>81.59999999999999</v>
@@ -5293,37 +5293,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M49">
-        <v>24.9282548</v>
+        <v>25.4586432</v>
       </c>
       <c r="N49">
-        <v>-2.903254800000013</v>
+        <v>-3.433643200000013</v>
       </c>
       <c r="O49">
-        <v>-0.7490397384000035</v>
+        <v>-0.8858799456000034</v>
       </c>
       <c r="P49">
-        <v>-2.15421506160001</v>
+        <v>-2.54776325440001</v>
       </c>
       <c r="Q49">
-        <v>29.44578493839999</v>
+        <v>29.05223674559999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1326753003291398</v>
+        <v>0.1343459791816233</v>
       </c>
       <c r="T49">
-        <v>2.006357975268819</v>
+        <v>2.044941782485527</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2279521789868738</v>
+        <v>0.2232031752579806</v>
       </c>
       <c r="W49">
-        <v>0.1133366201247269</v>
+        <v>0.1140337738721285</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8835355774685032</v>
+        <v>0.8651285862712428</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1245961206330658</v>
+        <v>0.1256061206330658</v>
       </c>
       <c r="C50">
-        <v>126.3066563863916</v>
+        <v>121.4363189750634</v>
       </c>
       <c r="D50">
-        <v>218.1306563863916</v>
+        <v>216.8733189750634</v>
       </c>
       <c r="E50">
-        <v>-20.976</v>
+        <v>-17.363</v>
       </c>
       <c r="F50">
-        <v>173.424</v>
+        <v>177.037</v>
       </c>
       <c r="G50">
         <v>81.59999999999999</v>
@@ -5375,37 +5375,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M50">
-        <v>25.4586432</v>
+        <v>25.9890316</v>
       </c>
       <c r="N50">
-        <v>-3.433643200000013</v>
+        <v>-3.964031600000013</v>
       </c>
       <c r="O50">
-        <v>-0.8858799456000034</v>
+        <v>-1.022720152800003</v>
       </c>
       <c r="P50">
-        <v>-2.54776325440001</v>
+        <v>-2.941311447200009</v>
       </c>
       <c r="Q50">
-        <v>29.05223674559999</v>
+        <v>28.65868855279999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1343459791816233</v>
+        <v>0.1360821748518512</v>
       </c>
       <c r="T50">
-        <v>2.044941782485527</v>
+        <v>2.085038680181321</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2232031752579806</v>
+        <v>0.218648008415981</v>
       </c>
       <c r="W50">
-        <v>0.1140337738721285</v>
+        <v>0.114702472364534</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8651285862712428</v>
+        <v>0.8474729008371358</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1256061206330658</v>
+        <v>0.1266161206330658</v>
       </c>
       <c r="C51">
-        <v>121.4363189750634</v>
+        <v>116.5803934496234</v>
       </c>
       <c r="D51">
-        <v>216.8733189750634</v>
+        <v>215.6303934496234</v>
       </c>
       <c r="E51">
-        <v>-17.363</v>
+        <v>-13.75</v>
       </c>
       <c r="F51">
-        <v>177.037</v>
+        <v>180.65</v>
       </c>
       <c r="G51">
         <v>81.59999999999999</v>
@@ -5457,37 +5457,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M51">
-        <v>25.9890316</v>
+        <v>26.51942</v>
       </c>
       <c r="N51">
-        <v>-3.964031600000013</v>
+        <v>-4.494420000000012</v>
       </c>
       <c r="O51">
-        <v>-1.022720152800003</v>
+        <v>-1.159560360000003</v>
       </c>
       <c r="P51">
-        <v>-2.941311447200009</v>
+        <v>-3.334859640000009</v>
       </c>
       <c r="Q51">
-        <v>28.65868855279999</v>
+        <v>28.26514035999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1360821748518512</v>
+        <v>0.1378878183488882</v>
       </c>
       <c r="T51">
-        <v>2.085038680181321</v>
+        <v>2.126739453784948</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.218648008415981</v>
+        <v>0.2142750482476614</v>
       </c>
       <c r="W51">
-        <v>0.114702472364534</v>
+        <v>0.1153444229172433</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8474729008371358</v>
+        <v>0.830523442820393</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1266161206330658</v>
+        <v>0.1276261206330658</v>
       </c>
       <c r="C52">
-        <v>116.5803934496234</v>
+        <v>111.7386334336376</v>
       </c>
       <c r="D52">
-        <v>215.6303934496234</v>
+        <v>214.4016334336376</v>
       </c>
       <c r="E52">
-        <v>-13.75</v>
+        <v>-10.137</v>
       </c>
       <c r="F52">
-        <v>180.65</v>
+        <v>184.263</v>
       </c>
       <c r="G52">
         <v>81.59999999999999</v>
@@ -5539,37 +5539,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M52">
-        <v>26.51942</v>
+        <v>27.0498084</v>
       </c>
       <c r="N52">
-        <v>-4.494420000000012</v>
+        <v>-5.024808400000012</v>
       </c>
       <c r="O52">
-        <v>-1.159560360000003</v>
+        <v>-1.296400567200003</v>
       </c>
       <c r="P52">
-        <v>-3.334859640000009</v>
+        <v>-3.728407832800009</v>
       </c>
       <c r="Q52">
-        <v>28.26514035999999</v>
+        <v>27.87159216719999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1378878183488882</v>
+        <v>0.1397671615804982</v>
       </c>
       <c r="T52">
-        <v>2.126739453784948</v>
+        <v>2.170142299780559</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2142750482476614</v>
+        <v>0.2100735767133936</v>
       </c>
       <c r="W52">
-        <v>0.1153444229172433</v>
+        <v>0.1159611989384738</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.830523442820393</v>
+        <v>0.8142386694317579</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1276261206330658</v>
+        <v>0.1582019169397186</v>
       </c>
       <c r="C53">
-        <v>111.7386334336376</v>
+        <v>76.58102455571324</v>
       </c>
       <c r="D53">
-        <v>214.4016334336376</v>
+        <v>182.8570245557133</v>
       </c>
       <c r="E53">
-        <v>-10.137</v>
+        <v>-6.524000000000001</v>
       </c>
       <c r="F53">
-        <v>184.263</v>
+        <v>187.876</v>
       </c>
       <c r="G53">
         <v>81.59999999999999</v>
@@ -5621,45 +5621,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M53">
-        <v>27.0498084</v>
+        <v>37.7255008</v>
       </c>
       <c r="N53">
-        <v>-5.024808400000012</v>
+        <v>-15.70050080000001</v>
       </c>
       <c r="O53">
-        <v>-1.296400567200003</v>
+        <v>-4.050729206400002</v>
       </c>
       <c r="P53">
-        <v>-3.728407832800009</v>
+        <v>-11.6497715936</v>
       </c>
       <c r="Q53">
-        <v>27.87159216719999</v>
+        <v>19.9502284064</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1397671615804982</v>
+        <v>0.1448202197522854</v>
       </c>
       <c r="T53">
-        <v>2.170142299780559</v>
+        <v>2.286841102824143</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.2100735767133936</v>
+        <v>0.1506262310505895</v>
       </c>
       <c r="W53">
-        <v>0.1159611989384738</v>
+        <v>0.1705542528050416</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8142386694317579</v>
+        <v>0.583822600971277</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1582019169397186</v>
+        <v>0.1597519169397186</v>
       </c>
       <c r="C54">
-        <v>76.58102455571324</v>
+        <v>71.6142839184345</v>
       </c>
       <c r="D54">
-        <v>182.8570245557133</v>
+        <v>181.5032839184345</v>
       </c>
       <c r="E54">
-        <v>-6.524000000000001</v>
+        <v>-2.911000000000001</v>
       </c>
       <c r="F54">
-        <v>187.876</v>
+        <v>191.489</v>
       </c>
       <c r="G54">
         <v>81.59999999999999</v>
@@ -5703,37 +5703,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M54">
-        <v>37.7255008</v>
+        <v>38.4509912</v>
       </c>
       <c r="N54">
-        <v>-15.70050080000001</v>
+        <v>-16.42599120000001</v>
       </c>
       <c r="O54">
-        <v>-4.050729206400002</v>
+        <v>-4.237905729600003</v>
       </c>
       <c r="P54">
-        <v>-11.6497715936</v>
+        <v>-12.18808547040001</v>
       </c>
       <c r="Q54">
-        <v>19.9502284064</v>
+        <v>19.41191452959999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1448202197522854</v>
+        <v>0.1469270329385042</v>
       </c>
       <c r="T54">
-        <v>2.286841102824143</v>
+        <v>2.335497296501252</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1506262310505895</v>
+        <v>0.1477842266911444</v>
       </c>
       <c r="W54">
-        <v>0.1705542528050416</v>
+        <v>0.1711249272804182</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.583822600971277</v>
+        <v>0.5728070801982339</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1597519169397186</v>
+        <v>0.1613019169397186</v>
       </c>
       <c r="C55">
-        <v>71.6142839184345</v>
+        <v>66.6674402042384</v>
       </c>
       <c r="D55">
-        <v>181.5032839184345</v>
+        <v>180.1694402042384</v>
       </c>
       <c r="E55">
-        <v>-2.911000000000001</v>
+        <v>0.7020000000000266</v>
       </c>
       <c r="F55">
-        <v>191.489</v>
+        <v>195.102</v>
       </c>
       <c r="G55">
         <v>81.59999999999999</v>
@@ -5785,37 +5785,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M55">
-        <v>38.4509912</v>
+        <v>39.17648160000001</v>
       </c>
       <c r="N55">
-        <v>-16.42599120000001</v>
+        <v>-17.15148160000002</v>
       </c>
       <c r="O55">
-        <v>-4.237905729600003</v>
+        <v>-4.425082252800005</v>
       </c>
       <c r="P55">
-        <v>-12.18808547040001</v>
+        <v>-12.72639934720001</v>
       </c>
       <c r="Q55">
-        <v>19.41191452959999</v>
+        <v>18.87360065279999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1469270329385042</v>
+        <v>0.1491254466980369</v>
       </c>
       <c r="T55">
-        <v>2.335497296501252</v>
+        <v>2.386268976859975</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1477842266911444</v>
+        <v>0.1450474817524194</v>
       </c>
       <c r="W55">
-        <v>0.1711249272804182</v>
+        <v>0.1716744656641142</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5728070801982339</v>
+        <v>0.5621995416760444</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1613019169397186</v>
+        <v>0.1628519169397186</v>
       </c>
       <c r="C56">
-        <v>66.6674402042384</v>
+        <v>61.74005795366224</v>
       </c>
       <c r="D56">
-        <v>180.1694402042384</v>
+        <v>178.8550579536623</v>
       </c>
       <c r="E56">
-        <v>0.7020000000000266</v>
+        <v>4.315000000000026</v>
       </c>
       <c r="F56">
-        <v>195.102</v>
+        <v>198.715</v>
       </c>
       <c r="G56">
         <v>81.59999999999999</v>
@@ -5867,37 +5867,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M56">
-        <v>39.17648160000001</v>
+        <v>39.90197200000001</v>
       </c>
       <c r="N56">
-        <v>-17.15148160000002</v>
+        <v>-17.87697200000002</v>
       </c>
       <c r="O56">
-        <v>-4.425082252800005</v>
+        <v>-4.612258776000004</v>
       </c>
       <c r="P56">
-        <v>-12.72639934720001</v>
+        <v>-13.26471322400001</v>
       </c>
       <c r="Q56">
-        <v>18.87360065279999</v>
+        <v>18.33528677599999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1491254466980369</v>
+        <v>0.1514215677357711</v>
       </c>
       <c r="T56">
-        <v>2.386268976859975</v>
+        <v>2.439297176345753</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1450474817524194</v>
+        <v>0.1424102548114664</v>
       </c>
       <c r="W56">
-        <v>0.1716744656641142</v>
+        <v>0.1722040208338576</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5621995416760444</v>
+        <v>0.5519777318273891</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1628519169397186</v>
+        <v>0.1644019169397186</v>
       </c>
       <c r="C57">
-        <v>61.74005795366224</v>
+        <v>56.83171432236645</v>
       </c>
       <c r="D57">
-        <v>178.8550579536623</v>
+        <v>177.5597143223665</v>
       </c>
       <c r="E57">
-        <v>4.315000000000026</v>
+        <v>7.928000000000026</v>
       </c>
       <c r="F57">
-        <v>198.715</v>
+        <v>202.328</v>
       </c>
       <c r="G57">
         <v>81.59999999999999</v>
@@ -5949,37 +5949,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M57">
-        <v>39.90197200000001</v>
+        <v>40.62746240000001</v>
       </c>
       <c r="N57">
-        <v>-17.87697200000002</v>
+        <v>-18.60246240000001</v>
       </c>
       <c r="O57">
-        <v>-4.612258776000004</v>
+        <v>-4.799435299200004</v>
       </c>
       <c r="P57">
-        <v>-13.26471322400001</v>
+        <v>-13.80302710080001</v>
       </c>
       <c r="Q57">
-        <v>18.33528677599999</v>
+        <v>17.79697289919999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1514215677357711</v>
+        <v>0.153822057911584</v>
       </c>
       <c r="T57">
-        <v>2.439297176345753</v>
+        <v>2.494735748535429</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1424102548114664</v>
+        <v>0.1398672145469759</v>
       </c>
       <c r="W57">
-        <v>0.1722040208338576</v>
+        <v>0.1727146633189672</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5519777318273891</v>
+        <v>0.5421209866161857</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1644019169397186</v>
+        <v>0.1659519169397187</v>
       </c>
       <c r="C58">
-        <v>56.83171432236645</v>
+        <v>51.94199862759899</v>
       </c>
       <c r="D58">
-        <v>177.5597143223665</v>
+        <v>176.282998627599</v>
       </c>
       <c r="E58">
-        <v>7.928000000000026</v>
+        <v>11.54100000000003</v>
       </c>
       <c r="F58">
-        <v>202.328</v>
+        <v>205.941</v>
       </c>
       <c r="G58">
         <v>81.59999999999999</v>
@@ -6031,37 +6031,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M58">
-        <v>40.62746240000001</v>
+        <v>41.3529528</v>
       </c>
       <c r="N58">
-        <v>-18.60246240000001</v>
+        <v>-19.32795280000001</v>
       </c>
       <c r="O58">
-        <v>-4.799435299200004</v>
+        <v>-4.986611822400003</v>
       </c>
       <c r="P58">
-        <v>-13.80302710080001</v>
+        <v>-14.34134097760001</v>
       </c>
       <c r="Q58">
-        <v>17.79697289919999</v>
+        <v>17.25865902239999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.153822057911584</v>
+        <v>0.1563341987932488</v>
       </c>
       <c r="T58">
-        <v>2.494735748535429</v>
+        <v>2.552752858966485</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1398672145469759</v>
+        <v>0.13741340376545</v>
       </c>
       <c r="W58">
-        <v>0.1727146633189672</v>
+        <v>0.1732073885238977</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5421209866161857</v>
+        <v>0.5326100921141474</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1659519169397187</v>
+        <v>0.1675019169397187</v>
       </c>
       <c r="C59">
-        <v>51.94199862759899</v>
+        <v>47.07051191408669</v>
       </c>
       <c r="D59">
-        <v>176.282998627599</v>
+        <v>175.0245119140867</v>
       </c>
       <c r="E59">
-        <v>11.54100000000003</v>
+        <v>15.15400000000002</v>
       </c>
       <c r="F59">
-        <v>205.941</v>
+        <v>209.554</v>
       </c>
       <c r="G59">
         <v>81.59999999999999</v>
@@ -6113,37 +6113,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M59">
-        <v>41.3529528</v>
+        <v>42.07844320000001</v>
       </c>
       <c r="N59">
-        <v>-19.32795280000001</v>
+        <v>-20.05344320000002</v>
       </c>
       <c r="O59">
-        <v>-4.986611822400003</v>
+        <v>-5.173788345600005</v>
       </c>
       <c r="P59">
-        <v>-14.34134097760001</v>
+        <v>-14.87965485440001</v>
       </c>
       <c r="Q59">
-        <v>17.25865902239999</v>
+        <v>16.72034514559999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1563341987932488</v>
+        <v>0.1589659654311833</v>
       </c>
       <c r="T59">
-        <v>2.552752858966485</v>
+        <v>2.613532688941878</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.13741340376545</v>
+        <v>0.1350442071488043</v>
       </c>
       <c r="W59">
-        <v>0.1732073885238977</v>
+        <v>0.1736831232045201</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5326100921141474</v>
+        <v>0.5234271594914897</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1675019169397186</v>
+        <v>0.1690519169397186</v>
       </c>
       <c r="C60">
-        <v>47.07051191408672</v>
+        <v>42.21686653838967</v>
       </c>
       <c r="D60">
-        <v>175.0245119140868</v>
+        <v>173.7838665383897</v>
       </c>
       <c r="E60">
-        <v>15.154</v>
+        <v>18.767</v>
       </c>
       <c r="F60">
-        <v>209.554</v>
+        <v>213.167</v>
       </c>
       <c r="G60">
         <v>81.59999999999999</v>
@@ -6195,37 +6195,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M60">
-        <v>42.0784432</v>
+        <v>42.8039336</v>
       </c>
       <c r="N60">
-        <v>-20.05344320000001</v>
+        <v>-20.77893360000001</v>
       </c>
       <c r="O60">
-        <v>-5.173788345600003</v>
+        <v>-5.360964868800003</v>
       </c>
       <c r="P60">
-        <v>-14.87965485440001</v>
+        <v>-15.41796873120001</v>
       </c>
       <c r="Q60">
-        <v>16.72034514559999</v>
+        <v>16.1820312688</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1589659654311833</v>
+        <v>0.1617261109295048</v>
       </c>
       <c r="T60">
-        <v>2.613532688941878</v>
+        <v>2.677277388672167</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1350442071488043</v>
+        <v>0.1327553222818755</v>
       </c>
       <c r="W60">
-        <v>0.1736831232045201</v>
+        <v>0.1741427312857994</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5234271594914897</v>
+        <v>0.5145555127204475</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1690519169397186</v>
+        <v>0.1706019169397186</v>
       </c>
       <c r="C61">
-        <v>42.21686653838967</v>
+        <v>37.38068577080799</v>
       </c>
       <c r="D61">
-        <v>173.7838665383897</v>
+        <v>172.560685770808</v>
       </c>
       <c r="E61">
-        <v>18.767</v>
+        <v>22.38</v>
       </c>
       <c r="F61">
-        <v>213.167</v>
+        <v>216.78</v>
       </c>
       <c r="G61">
         <v>81.59999999999999</v>
@@ -6277,37 +6277,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M61">
-        <v>42.8039336</v>
+        <v>43.529424</v>
       </c>
       <c r="N61">
-        <v>-20.77893360000001</v>
+        <v>-21.50442400000001</v>
       </c>
       <c r="O61">
-        <v>-5.360964868800003</v>
+        <v>-5.548141392000002</v>
       </c>
       <c r="P61">
-        <v>-15.41796873120001</v>
+        <v>-15.95628260800001</v>
       </c>
       <c r="Q61">
-        <v>16.1820312688</v>
+        <v>15.643717392</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1617261109295048</v>
+        <v>0.1646242637027424</v>
       </c>
       <c r="T61">
-        <v>2.677277388672167</v>
+        <v>2.744209323388971</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1327553222818755</v>
+        <v>0.1305427335771775</v>
       </c>
       <c r="W61">
-        <v>0.1741427312857994</v>
+        <v>0.1745870190977027</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5145555127204475</v>
+        <v>0.5059795875084401</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1706019169397186</v>
+        <v>0.1941014536958822</v>
       </c>
       <c r="C62">
-        <v>37.38068577080799</v>
+        <v>17.12909803470413</v>
       </c>
       <c r="D62">
-        <v>172.560685770808</v>
+        <v>155.9220980347041</v>
       </c>
       <c r="E62">
-        <v>22.38</v>
+        <v>25.99299999999999</v>
       </c>
       <c r="F62">
-        <v>216.78</v>
+        <v>220.393</v>
       </c>
       <c r="G62">
         <v>81.59999999999999</v>
@@ -6359,45 +6359,45 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M62">
-        <v>43.529424</v>
+        <v>51.9686694</v>
       </c>
       <c r="N62">
-        <v>-21.50442400000001</v>
+        <v>-29.94366940000001</v>
       </c>
       <c r="O62">
-        <v>-5.548141392000002</v>
+        <v>-7.725466705200003</v>
       </c>
       <c r="P62">
-        <v>-15.95628260800001</v>
+        <v>-22.21820269480001</v>
       </c>
       <c r="Q62">
-        <v>15.643717392</v>
+        <v>9.381797305199992</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1646242637027424</v>
+        <v>0.1692083134288733</v>
       </c>
       <c r="T62">
-        <v>2.744209323388971</v>
+        <v>2.850076522606774</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1305427335771775</v>
+        <v>0.1093437654957546</v>
       </c>
       <c r="W62">
-        <v>0.1745870190977027</v>
+        <v>0.2100167400961011</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5059795875084401</v>
+        <v>0.4238130445571884</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1941014536958822</v>
+        <v>0.1960014536958822</v>
       </c>
       <c r="C63">
-        <v>17.12909803470413</v>
+        <v>12.30994069174946</v>
       </c>
       <c r="D63">
-        <v>155.9220980347041</v>
+        <v>154.7159406917495</v>
       </c>
       <c r="E63">
-        <v>25.99299999999999</v>
+        <v>29.60599999999999</v>
       </c>
       <c r="F63">
-        <v>220.393</v>
+        <v>224.006</v>
       </c>
       <c r="G63">
         <v>81.59999999999999</v>
@@ -6441,37 +6441,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M63">
-        <v>51.9686694</v>
+        <v>52.8206148</v>
       </c>
       <c r="N63">
-        <v>-29.94366940000001</v>
+        <v>-30.79561480000001</v>
       </c>
       <c r="O63">
-        <v>-7.725466705200003</v>
+        <v>-7.945268618400003</v>
       </c>
       <c r="P63">
-        <v>-22.21820269480001</v>
+        <v>-22.85034618160001</v>
       </c>
       <c r="Q63">
-        <v>9.381797305199992</v>
+        <v>8.749653818399995</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1692083134288733</v>
+        <v>0.1724559006243699</v>
       </c>
       <c r="T63">
-        <v>2.850076522606774</v>
+        <v>2.925078536359583</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1093437654957546</v>
+        <v>0.1075801563748553</v>
       </c>
       <c r="W63">
-        <v>0.2100167400961011</v>
+        <v>0.2104325991268091</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4238130445571884</v>
+        <v>0.4169773502901369</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1960014536958822</v>
+        <v>0.1979014536958822</v>
       </c>
       <c r="C64">
-        <v>12.30994069174946</v>
+        <v>7.509300903546091</v>
       </c>
       <c r="D64">
-        <v>154.7159406917495</v>
+        <v>153.5283009035461</v>
       </c>
       <c r="E64">
-        <v>29.60599999999999</v>
+        <v>33.21899999999999</v>
       </c>
       <c r="F64">
-        <v>224.006</v>
+        <v>227.619</v>
       </c>
       <c r="G64">
         <v>81.59999999999999</v>
@@ -6523,37 +6523,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M64">
-        <v>52.8206148</v>
+        <v>53.6725602</v>
       </c>
       <c r="N64">
-        <v>-30.79561480000001</v>
+        <v>-31.64756020000001</v>
       </c>
       <c r="O64">
-        <v>-7.945268618400003</v>
+        <v>-8.165070531600003</v>
       </c>
       <c r="P64">
-        <v>-22.85034618160001</v>
+        <v>-23.48248966840001</v>
       </c>
       <c r="Q64">
-        <v>8.749653818399995</v>
+        <v>8.117510331599995</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1724559006243699</v>
+        <v>0.1758790330736772</v>
       </c>
       <c r="T64">
-        <v>2.925078536359583</v>
+        <v>3.004134713017951</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1075801563748553</v>
+        <v>0.1058725348450957</v>
       </c>
       <c r="W64">
-        <v>0.2104325991268091</v>
+        <v>0.2108352562835264</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4169773502901369</v>
+        <v>0.4103586621902935</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1979014536958822</v>
+        <v>0.1998014536958823</v>
       </c>
       <c r="C65">
-        <v>7.509300903546091</v>
+        <v>2.726755481901506</v>
       </c>
       <c r="D65">
-        <v>153.5283009035461</v>
+        <v>152.3587554819015</v>
       </c>
       <c r="E65">
-        <v>33.21899999999999</v>
+        <v>36.83199999999999</v>
       </c>
       <c r="F65">
-        <v>227.619</v>
+        <v>231.232</v>
       </c>
       <c r="G65">
         <v>81.59999999999999</v>
@@ -6605,37 +6605,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M65">
-        <v>53.6725602</v>
+        <v>54.5245056</v>
       </c>
       <c r="N65">
-        <v>-31.64756020000001</v>
+        <v>-32.49950560000001</v>
       </c>
       <c r="O65">
-        <v>-8.165070531600003</v>
+        <v>-8.384872444800004</v>
       </c>
       <c r="P65">
-        <v>-23.48248966840001</v>
+        <v>-24.11463315520001</v>
       </c>
       <c r="Q65">
-        <v>8.117510331599995</v>
+        <v>7.485366844799991</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1758790330736772</v>
+        <v>0.1794923395479461</v>
       </c>
       <c r="T65">
-        <v>3.004134713017951</v>
+        <v>3.087582899490672</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1058725348450957</v>
+        <v>0.1042182764881411</v>
       </c>
       <c r="W65">
-        <v>0.2108352562835264</v>
+        <v>0.2112253304040963</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4103586621902935</v>
+        <v>0.4039468080935701</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1998014536958823</v>
+        <v>0.2017014536958823</v>
       </c>
       <c r="C66">
-        <v>2.726755481901506</v>
+        <v>-2.038105963840565</v>
       </c>
       <c r="D66">
-        <v>152.3587554819015</v>
+        <v>151.2068940361595</v>
       </c>
       <c r="E66">
-        <v>36.83199999999999</v>
+        <v>40.44500000000002</v>
       </c>
       <c r="F66">
-        <v>231.232</v>
+        <v>234.845</v>
       </c>
       <c r="G66">
         <v>81.59999999999999</v>
@@ -6687,37 +6687,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M66">
-        <v>54.5245056</v>
+        <v>55.37645100000001</v>
       </c>
       <c r="N66">
-        <v>-32.49950560000001</v>
+        <v>-33.35145100000002</v>
       </c>
       <c r="O66">
-        <v>-8.384872444800004</v>
+        <v>-8.604674358000006</v>
       </c>
       <c r="P66">
-        <v>-24.11463315520001</v>
+        <v>-24.74677664200001</v>
       </c>
       <c r="Q66">
-        <v>7.485366844799991</v>
+        <v>6.853223357999987</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1794923395479461</v>
+        <v>0.1833121206778874</v>
       </c>
       <c r="T66">
-        <v>3.087582899490672</v>
+        <v>3.175799553761834</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1042182764881411</v>
+        <v>0.1026149183883235</v>
       </c>
       <c r="W66">
-        <v>0.2112253304040963</v>
+        <v>0.2116034022440333</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4039468080935701</v>
+        <v>0.3977322418152075</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2017014536958823</v>
+        <v>0.2036014536958822</v>
       </c>
       <c r="C67">
-        <v>-2.038105963840565</v>
+        <v>-6.785681506929876</v>
       </c>
       <c r="D67">
-        <v>151.2068940361595</v>
+        <v>150.0723184930702</v>
       </c>
       <c r="E67">
-        <v>40.44500000000002</v>
+        <v>44.05800000000002</v>
       </c>
       <c r="F67">
-        <v>234.845</v>
+        <v>238.458</v>
       </c>
       <c r="G67">
         <v>81.59999999999999</v>
@@ -6769,37 +6769,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M67">
-        <v>55.37645100000001</v>
+        <v>56.22839640000001</v>
       </c>
       <c r="N67">
-        <v>-33.35145100000002</v>
+        <v>-34.20339640000002</v>
       </c>
       <c r="O67">
-        <v>-8.604674358000006</v>
+        <v>-8.824476271200005</v>
       </c>
       <c r="P67">
-        <v>-24.74677664200001</v>
+        <v>-25.37892012880001</v>
       </c>
       <c r="Q67">
-        <v>6.853223357999987</v>
+        <v>6.22107987119999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1833121206778874</v>
+        <v>0.1873565948154723</v>
       </c>
       <c r="T67">
-        <v>3.175799553761834</v>
+        <v>3.269205422990123</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1026149183883235</v>
+        <v>0.1010601468975914</v>
       </c>
       <c r="W67">
-        <v>0.2116034022440333</v>
+        <v>0.211970017361548</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3977322418152075</v>
+        <v>0.3917059957270983</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2036014536958822</v>
+        <v>0.2055014536958822</v>
       </c>
       <c r="C68">
-        <v>-6.785681506929876</v>
+        <v>-11.51635736188396</v>
       </c>
       <c r="D68">
-        <v>150.0723184930702</v>
+        <v>148.9546426381161</v>
       </c>
       <c r="E68">
-        <v>44.05800000000002</v>
+        <v>47.67100000000002</v>
       </c>
       <c r="F68">
-        <v>238.458</v>
+        <v>242.071</v>
       </c>
       <c r="G68">
         <v>81.59999999999999</v>
@@ -6851,37 +6851,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M68">
-        <v>56.22839640000001</v>
+        <v>57.08034180000001</v>
       </c>
       <c r="N68">
-        <v>-34.20339640000002</v>
+        <v>-35.05534180000001</v>
       </c>
       <c r="O68">
-        <v>-8.824476271200005</v>
+        <v>-9.044278184400005</v>
       </c>
       <c r="P68">
-        <v>-25.37892012880001</v>
+        <v>-26.01106361560001</v>
       </c>
       <c r="Q68">
-        <v>6.22107987119999</v>
+        <v>5.588936384399993</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1873565948154723</v>
+        <v>0.1916461885977593</v>
       </c>
       <c r="T68">
-        <v>3.269205422990123</v>
+        <v>3.368272253989824</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1010601468975914</v>
+        <v>0.09955178649613478</v>
       </c>
       <c r="W68">
-        <v>0.211970017361548</v>
+        <v>0.2123256887442114</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3917059957270983</v>
+        <v>0.3858596375819178</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2055014536958822</v>
+        <v>0.2074014536958823</v>
       </c>
       <c r="C69">
-        <v>-11.51635736188396</v>
+        <v>-16.23050832281797</v>
       </c>
       <c r="D69">
-        <v>148.9546426381161</v>
+        <v>147.8534916771821</v>
       </c>
       <c r="E69">
-        <v>47.67100000000002</v>
+        <v>51.28400000000002</v>
       </c>
       <c r="F69">
-        <v>242.071</v>
+        <v>245.684</v>
       </c>
       <c r="G69">
         <v>81.59999999999999</v>
@@ -6933,37 +6933,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M69">
-        <v>57.08034180000001</v>
+        <v>57.93228720000001</v>
       </c>
       <c r="N69">
-        <v>-35.05534180000001</v>
+        <v>-35.90728720000002</v>
       </c>
       <c r="O69">
-        <v>-9.044278184400005</v>
+        <v>-9.264080097600006</v>
       </c>
       <c r="P69">
-        <v>-26.01106361560001</v>
+        <v>-26.64320710240001</v>
       </c>
       <c r="Q69">
-        <v>5.588936384399993</v>
+        <v>4.956792897599989</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1916461885977593</v>
+        <v>0.1962038819914394</v>
       </c>
       <c r="T69">
-        <v>3.368272253989824</v>
+        <v>3.473530761927007</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09955178649613478</v>
+        <v>0.09808778963589748</v>
       </c>
       <c r="W69">
-        <v>0.2123256887442114</v>
+        <v>0.2126708992038554</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3858596375819178</v>
+        <v>0.3801852311468895</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2074014536958823</v>
+        <v>0.2093014536958823</v>
       </c>
       <c r="C70">
-        <v>-16.23050832281797</v>
+        <v>-20.92849818247512</v>
       </c>
       <c r="D70">
-        <v>147.8534916771821</v>
+        <v>146.7685018175249</v>
       </c>
       <c r="E70">
-        <v>51.28400000000002</v>
+        <v>54.89700000000002</v>
       </c>
       <c r="F70">
-        <v>245.684</v>
+        <v>249.297</v>
       </c>
       <c r="G70">
         <v>81.59999999999999</v>
@@ -7015,37 +7015,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M70">
-        <v>57.93228720000001</v>
+        <v>58.78423260000001</v>
       </c>
       <c r="N70">
-        <v>-35.90728720000002</v>
+        <v>-36.75923260000002</v>
       </c>
       <c r="O70">
-        <v>-9.264080097600006</v>
+        <v>-9.483882010800006</v>
       </c>
       <c r="P70">
-        <v>-26.64320710240001</v>
+        <v>-27.27535058920001</v>
       </c>
       <c r="Q70">
-        <v>4.956792897599989</v>
+        <v>4.324649410799989</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1962038819914394</v>
+        <v>0.2010556201201955</v>
       </c>
       <c r="T70">
-        <v>3.473530761927007</v>
+        <v>3.585580141344006</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09808778963589748</v>
+        <v>0.09666622746726129</v>
       </c>
       <c r="W70">
-        <v>0.2126708992038554</v>
+        <v>0.2130061035632198</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3801852311468895</v>
+        <v>0.3746753002607027</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2093014536958823</v>
+        <v>0.2112014536958823</v>
       </c>
       <c r="C71">
-        <v>-20.92849818247512</v>
+        <v>-25.61068013294172</v>
       </c>
       <c r="D71">
-        <v>146.7685018175249</v>
+        <v>145.6993198670583</v>
       </c>
       <c r="E71">
-        <v>54.89700000000002</v>
+        <v>58.51000000000002</v>
       </c>
       <c r="F71">
-        <v>249.297</v>
+        <v>252.91</v>
       </c>
       <c r="G71">
         <v>81.59999999999999</v>
@@ -7097,37 +7097,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M71">
-        <v>58.78423260000001</v>
+        <v>59.63617800000001</v>
       </c>
       <c r="N71">
-        <v>-36.75923260000002</v>
+        <v>-37.61117800000002</v>
       </c>
       <c r="O71">
-        <v>-9.483882010800006</v>
+        <v>-9.703683924000005</v>
       </c>
       <c r="P71">
-        <v>-27.27535058920001</v>
+        <v>-27.90749407600001</v>
       </c>
       <c r="Q71">
-        <v>4.324649410799989</v>
+        <v>3.692505923999988</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2010556201201955</v>
+        <v>0.2062308074575353</v>
       </c>
       <c r="T71">
-        <v>3.585580141344006</v>
+        <v>3.705099479388807</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09666622746726129</v>
+        <v>0.09528528136058614</v>
       </c>
       <c r="W71">
-        <v>0.2130061035632198</v>
+        <v>0.2133317306551738</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3746753002607027</v>
+        <v>0.3693227959712641</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2112014536958823</v>
+        <v>0.2131014536958823</v>
       </c>
       <c r="C72">
-        <v>-25.61068013294172</v>
+        <v>-30.27739714897388</v>
       </c>
       <c r="D72">
-        <v>145.6993198670583</v>
+        <v>144.6456028510262</v>
       </c>
       <c r="E72">
-        <v>58.51000000000002</v>
+        <v>62.12300000000002</v>
       </c>
       <c r="F72">
-        <v>252.91</v>
+        <v>256.523</v>
       </c>
       <c r="G72">
         <v>81.59999999999999</v>
@@ -7179,37 +7179,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M72">
-        <v>59.63617800000001</v>
+        <v>60.48812340000001</v>
       </c>
       <c r="N72">
-        <v>-37.61117800000002</v>
+        <v>-38.46312340000001</v>
       </c>
       <c r="O72">
-        <v>-9.703683924000005</v>
+        <v>-9.923485837200005</v>
       </c>
       <c r="P72">
-        <v>-27.90749407600001</v>
+        <v>-28.53963756280001</v>
       </c>
       <c r="Q72">
-        <v>3.692505923999988</v>
+        <v>3.060362437199991</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2062308074575353</v>
+        <v>0.2117629042664158</v>
       </c>
       <c r="T72">
-        <v>3.705099479388807</v>
+        <v>3.832861530402214</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09528528136058614</v>
+        <v>0.09394323514423987</v>
       </c>
       <c r="W72">
-        <v>0.2133317306551738</v>
+        <v>0.2136481851529883</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3693227959712641</v>
+        <v>0.3641210664505421</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2131014536958822</v>
+        <v>0.2150014536958822</v>
       </c>
       <c r="C73">
-        <v>-30.27739714897382</v>
+        <v>-34.92898235481036</v>
       </c>
       <c r="D73">
-        <v>144.6456028510262</v>
+        <v>143.6070176451897</v>
       </c>
       <c r="E73">
-        <v>62.12299999999996</v>
+        <v>65.73600000000002</v>
       </c>
       <c r="F73">
-        <v>256.523</v>
+        <v>260.136</v>
       </c>
       <c r="G73">
         <v>81.59999999999999</v>
@@ -7261,37 +7261,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M73">
-        <v>60.48812339999999</v>
+        <v>61.34006880000001</v>
       </c>
       <c r="N73">
-        <v>-38.4631234</v>
+        <v>-39.31506880000002</v>
       </c>
       <c r="O73">
-        <v>-9.923485837200001</v>
+        <v>-10.14328775040001</v>
       </c>
       <c r="P73">
-        <v>-28.5396375628</v>
+        <v>-29.17178104960001</v>
       </c>
       <c r="Q73">
-        <v>3.060362437200002</v>
+        <v>2.428218950399987</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2117629042664158</v>
+        <v>0.2176901508473592</v>
       </c>
       <c r="T73">
-        <v>3.832861530402213</v>
+        <v>3.969749442202292</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09394323514423988</v>
+        <v>0.09263846798945874</v>
       </c>
       <c r="W73">
-        <v>0.2136481851529883</v>
+        <v>0.2139558492480856</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3641210664505422</v>
+        <v>0.3590638294165067</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2150014536958822</v>
+        <v>0.2169014536958822</v>
       </c>
       <c r="C74">
-        <v>-34.92898235481036</v>
+        <v>-39.5657593752951</v>
       </c>
       <c r="D74">
-        <v>143.6070176451897</v>
+        <v>142.5832406247049</v>
       </c>
       <c r="E74">
-        <v>65.73600000000002</v>
+        <v>69.34900000000002</v>
       </c>
       <c r="F74">
-        <v>260.136</v>
+        <v>263.749</v>
       </c>
       <c r="G74">
         <v>81.59999999999999</v>
@@ -7343,37 +7343,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M74">
-        <v>61.34006880000001</v>
+        <v>62.19201420000001</v>
       </c>
       <c r="N74">
-        <v>-39.31506880000002</v>
+        <v>-40.16701420000002</v>
       </c>
       <c r="O74">
-        <v>-10.14328775040001</v>
+        <v>-10.36308966360001</v>
       </c>
       <c r="P74">
-        <v>-29.17178104960001</v>
+        <v>-29.80392453640001</v>
       </c>
       <c r="Q74">
-        <v>2.428218950399987</v>
+        <v>1.79607546359999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2176901508473592</v>
+        <v>0.2240564527305947</v>
       </c>
       <c r="T74">
-        <v>3.969749442202292</v>
+        <v>4.116777199320895</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09263846798945874</v>
+        <v>0.0913694478800141</v>
       </c>
       <c r="W74">
-        <v>0.2139558492480856</v>
+        <v>0.2142550841898927</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3590638294165067</v>
+        <v>0.3541451468217601</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2169014536958822</v>
+        <v>0.2188014536958822</v>
       </c>
       <c r="C75">
-        <v>-39.5657593752951</v>
+        <v>-44.18804267208716</v>
       </c>
       <c r="D75">
-        <v>142.5832406247049</v>
+        <v>141.5739573279129</v>
       </c>
       <c r="E75">
-        <v>69.34900000000002</v>
+        <v>72.96200000000002</v>
       </c>
       <c r="F75">
-        <v>263.749</v>
+        <v>267.362</v>
       </c>
       <c r="G75">
         <v>81.59999999999999</v>
@@ -7425,37 +7425,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M75">
-        <v>62.19201420000001</v>
+        <v>63.04395960000001</v>
       </c>
       <c r="N75">
-        <v>-40.16701420000002</v>
+        <v>-41.01895960000002</v>
       </c>
       <c r="O75">
-        <v>-10.36308966360001</v>
+        <v>-10.58289157680001</v>
       </c>
       <c r="P75">
-        <v>-29.80392453640001</v>
+        <v>-30.43606802320001</v>
       </c>
       <c r="Q75">
-        <v>1.79607546359999</v>
+        <v>1.16393197679999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2240564527305947</v>
+        <v>0.2309124701433099</v>
       </c>
       <c r="T75">
-        <v>4.116777199320895</v>
+        <v>4.27511478391016</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0913694478800141</v>
+        <v>0.09013472561136526</v>
       </c>
       <c r="W75">
-        <v>0.2142550841898927</v>
+        <v>0.2145462317008401</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3541451468217601</v>
+        <v>0.349359401594439</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2188014536958822</v>
+        <v>0.2207014536958822</v>
       </c>
       <c r="C76">
-        <v>-44.18804267208716</v>
+        <v>-48.79613786569161</v>
       </c>
       <c r="D76">
-        <v>141.5739573279129</v>
+        <v>140.5788621343084</v>
       </c>
       <c r="E76">
-        <v>72.96200000000002</v>
+        <v>76.57500000000002</v>
       </c>
       <c r="F76">
-        <v>267.362</v>
+        <v>270.975</v>
       </c>
       <c r="G76">
         <v>81.59999999999999</v>
@@ -7507,37 +7507,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M76">
-        <v>63.04395960000001</v>
+        <v>63.89590500000001</v>
       </c>
       <c r="N76">
-        <v>-41.01895960000002</v>
+        <v>-41.87090500000001</v>
       </c>
       <c r="O76">
-        <v>-10.58289157680001</v>
+        <v>-10.80269349</v>
       </c>
       <c r="P76">
-        <v>-30.43606802320001</v>
+        <v>-31.06821151000001</v>
       </c>
       <c r="Q76">
-        <v>1.16393197679999</v>
+        <v>0.5317884899999896</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2309124701433099</v>
+        <v>0.2383169689490423</v>
       </c>
       <c r="T76">
-        <v>4.27511478391016</v>
+        <v>4.446119375266568</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09013472561136526</v>
+        <v>0.08893292926988039</v>
       </c>
       <c r="W76">
-        <v>0.2145462317008401</v>
+        <v>0.2148296152781622</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.349359401594439</v>
+        <v>0.3447012762398465</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2207014536958822</v>
+        <v>0.2226014536958822</v>
       </c>
       <c r="C77">
-        <v>-48.79613786569161</v>
+        <v>-53.39034204400451</v>
       </c>
       <c r="D77">
-        <v>140.5788621343084</v>
+        <v>139.5976579559955</v>
       </c>
       <c r="E77">
-        <v>76.57500000000002</v>
+        <v>80.18800000000002</v>
       </c>
       <c r="F77">
-        <v>270.975</v>
+        <v>274.588</v>
       </c>
       <c r="G77">
         <v>81.59999999999999</v>
@@ -7589,37 +7589,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M77">
-        <v>63.89590500000001</v>
+        <v>64.7478504</v>
       </c>
       <c r="N77">
-        <v>-41.87090500000001</v>
+        <v>-42.72285040000001</v>
       </c>
       <c r="O77">
-        <v>-10.80269349</v>
+        <v>-11.0224954032</v>
       </c>
       <c r="P77">
-        <v>-31.06821151000001</v>
+        <v>-31.70035499680001</v>
       </c>
       <c r="Q77">
-        <v>0.5317884899999896</v>
+        <v>-0.1003549968000073</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2383169689490423</v>
+        <v>0.2463385093219191</v>
       </c>
       <c r="T77">
-        <v>4.446119375266568</v>
+        <v>4.631374349236008</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08893292926988039</v>
+        <v>0.08776275914790829</v>
       </c>
       <c r="W77">
-        <v>0.2148296152781622</v>
+        <v>0.2151055413929232</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3447012762398465</v>
+        <v>0.3401657331314275</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2226014536958822</v>
+        <v>0.2245014536958822</v>
       </c>
       <c r="C78">
-        <v>-53.39034204400451</v>
+        <v>-57.97094405802608</v>
       </c>
       <c r="D78">
-        <v>139.5976579559955</v>
+        <v>138.6300559419739</v>
       </c>
       <c r="E78">
-        <v>80.18800000000002</v>
+        <v>83.80100000000002</v>
       </c>
       <c r="F78">
-        <v>274.588</v>
+        <v>278.201</v>
       </c>
       <c r="G78">
         <v>81.59999999999999</v>
@@ -7671,37 +7671,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M78">
-        <v>64.7478504</v>
+        <v>65.59979580000001</v>
       </c>
       <c r="N78">
-        <v>-42.72285040000001</v>
+        <v>-43.57479580000002</v>
       </c>
       <c r="O78">
-        <v>-11.0224954032</v>
+        <v>-11.24229731640001</v>
       </c>
       <c r="P78">
-        <v>-31.70035499680001</v>
+        <v>-32.33249848360001</v>
       </c>
       <c r="Q78">
-        <v>-0.1003549968000073</v>
+        <v>-0.7324984836000112</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2463385093219191</v>
+        <v>0.2550575749446112</v>
       </c>
       <c r="T78">
-        <v>4.631374349236008</v>
+        <v>4.832738451376703</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08776275914790829</v>
+        <v>0.0866229830550783</v>
       </c>
       <c r="W78">
-        <v>0.2151055413929232</v>
+        <v>0.2153743005956126</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3401657331314275</v>
+        <v>0.3357479963375128</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2245014536958822</v>
+        <v>0.2264014536958822</v>
       </c>
       <c r="C79">
-        <v>-57.97094405802608</v>
+        <v>-62.53822480536004</v>
       </c>
       <c r="D79">
-        <v>138.6300559419739</v>
+        <v>137.67577519464</v>
       </c>
       <c r="E79">
-        <v>83.80100000000002</v>
+        <v>87.41400000000002</v>
       </c>
       <c r="F79">
-        <v>278.201</v>
+        <v>281.814</v>
       </c>
       <c r="G79">
         <v>81.59999999999999</v>
@@ -7753,37 +7753,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M79">
-        <v>65.59979580000001</v>
+        <v>66.4517412</v>
       </c>
       <c r="N79">
-        <v>-43.57479580000002</v>
+        <v>-44.42674120000001</v>
       </c>
       <c r="O79">
-        <v>-11.24229731640001</v>
+        <v>-11.4620992296</v>
       </c>
       <c r="P79">
-        <v>-32.33249848360001</v>
+        <v>-32.96464197040001</v>
       </c>
       <c r="Q79">
-        <v>-0.7324984836000112</v>
+        <v>-1.364641970400008</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2550575749446112</v>
+        <v>0.264569282896639</v>
       </c>
       <c r="T79">
-        <v>4.832738451376703</v>
+        <v>5.052408380984736</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0866229830550783</v>
+        <v>0.08551243199026963</v>
       </c>
       <c r="W79">
-        <v>0.2153743005956126</v>
+        <v>0.2156361685366944</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3357479963375128</v>
+        <v>0.3314435348460063</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2264014536958822</v>
+        <v>0.2283014536958823</v>
       </c>
       <c r="C80">
-        <v>-62.53822480536004</v>
+        <v>-67.09245750208416</v>
       </c>
       <c r="D80">
-        <v>137.67577519464</v>
+        <v>136.7345424979159</v>
       </c>
       <c r="E80">
-        <v>87.41400000000002</v>
+        <v>91.02700000000002</v>
       </c>
       <c r="F80">
-        <v>281.814</v>
+        <v>285.427</v>
       </c>
       <c r="G80">
         <v>81.59999999999999</v>
@@ -7835,37 +7835,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M80">
-        <v>66.4517412</v>
+        <v>67.30368660000001</v>
       </c>
       <c r="N80">
-        <v>-44.42674120000001</v>
+        <v>-45.27868660000001</v>
       </c>
       <c r="O80">
-        <v>-11.4620992296</v>
+        <v>-11.6819011428</v>
       </c>
       <c r="P80">
-        <v>-32.96464197040001</v>
+        <v>-33.59678545720001</v>
       </c>
       <c r="Q80">
-        <v>-1.364641970400008</v>
+        <v>-1.996785457200012</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.264569282896639</v>
+        <v>0.274986867796479</v>
       </c>
       <c r="T80">
-        <v>5.052408380984736</v>
+        <v>5.292999256269723</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08551243199026963</v>
+        <v>0.08442999614229152</v>
       </c>
       <c r="W80">
-        <v>0.2156361685366944</v>
+        <v>0.2158914069096477</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3314435348460063</v>
+        <v>0.3272480470631454</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2283014536958823</v>
+        <v>0.2302014536958822</v>
       </c>
       <c r="C81">
-        <v>-67.09245750208416</v>
+        <v>-71.6339079435445</v>
       </c>
       <c r="D81">
-        <v>136.7345424979159</v>
+        <v>135.8060920564555</v>
       </c>
       <c r="E81">
-        <v>91.02700000000002</v>
+        <v>94.64000000000001</v>
       </c>
       <c r="F81">
-        <v>285.427</v>
+        <v>289.04</v>
       </c>
       <c r="G81">
         <v>81.59999999999999</v>
@@ -7917,37 +7917,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M81">
-        <v>67.30368660000001</v>
+        <v>68.15563200000001</v>
       </c>
       <c r="N81">
-        <v>-45.27868660000001</v>
+        <v>-46.13063200000002</v>
       </c>
       <c r="O81">
-        <v>-11.6819011428</v>
+        <v>-11.90170305600001</v>
       </c>
       <c r="P81">
-        <v>-33.59678545720001</v>
+        <v>-34.22892894400002</v>
       </c>
       <c r="Q81">
-        <v>-1.996785457200012</v>
+        <v>-2.628928944000016</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.274986867796479</v>
+        <v>0.2864462111863029</v>
       </c>
       <c r="T81">
-        <v>5.292999256269723</v>
+        <v>5.55764921908321</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08442999614229152</v>
+        <v>0.08337462119051287</v>
       </c>
       <c r="W81">
-        <v>0.2158914069096477</v>
+        <v>0.2161402643232771</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3272480470631454</v>
+        <v>0.3231574464748561</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2302014536958822</v>
+        <v>0.2321014536958823</v>
       </c>
       <c r="C82">
-        <v>-71.6339079435445</v>
+        <v>-76.16283475459639</v>
       </c>
       <c r="D82">
-        <v>135.8060920564555</v>
+        <v>134.8901652454036</v>
       </c>
       <c r="E82">
-        <v>94.64000000000001</v>
+        <v>98.25300000000001</v>
       </c>
       <c r="F82">
-        <v>289.04</v>
+        <v>292.653</v>
       </c>
       <c r="G82">
         <v>81.59999999999999</v>
@@ -7999,37 +7999,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M82">
-        <v>68.15563200000001</v>
+        <v>69.0075774</v>
       </c>
       <c r="N82">
-        <v>-46.13063200000002</v>
+        <v>-46.98257740000001</v>
       </c>
       <c r="O82">
-        <v>-11.90170305600001</v>
+        <v>-12.1215049692</v>
       </c>
       <c r="P82">
-        <v>-34.22892894400002</v>
+        <v>-34.86107243080001</v>
       </c>
       <c r="Q82">
-        <v>-2.628928944000016</v>
+        <v>-3.261072430800006</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2864462111863029</v>
+        <v>0.2991118012487399</v>
       </c>
       <c r="T82">
-        <v>5.55764921908321</v>
+        <v>5.850157072719168</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08337462119051287</v>
+        <v>0.0823453048795189</v>
       </c>
       <c r="W82">
-        <v>0.2161402643232771</v>
+        <v>0.2163829771094095</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3231574464748561</v>
+        <v>0.3191678483702283</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2321014536958823</v>
+        <v>0.2340014536958823</v>
       </c>
       <c r="C83">
-        <v>-76.16283475459639</v>
+        <v>-80.67948962978673</v>
       </c>
       <c r="D83">
-        <v>134.8901652454036</v>
+        <v>133.9865103702133</v>
       </c>
       <c r="E83">
-        <v>98.25300000000001</v>
+        <v>101.866</v>
       </c>
       <c r="F83">
-        <v>292.653</v>
+        <v>296.266</v>
       </c>
       <c r="G83">
         <v>81.59999999999999</v>
@@ -8081,37 +8081,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M83">
-        <v>69.0075774</v>
+        <v>69.85952280000001</v>
       </c>
       <c r="N83">
-        <v>-46.98257740000001</v>
+        <v>-47.83452280000002</v>
       </c>
       <c r="O83">
-        <v>-12.1215049692</v>
+        <v>-12.3413068824</v>
       </c>
       <c r="P83">
-        <v>-34.86107243080001</v>
+        <v>-35.49321591760001</v>
       </c>
       <c r="Q83">
-        <v>-3.261072430800006</v>
+        <v>-3.89321591760001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2991118012487399</v>
+        <v>0.3131846790958922</v>
       </c>
       <c r="T83">
-        <v>5.850157072719168</v>
+        <v>6.175165798981345</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0823453048795189</v>
+        <v>0.08134109384440281</v>
       </c>
       <c r="W83">
-        <v>0.2163829771094095</v>
+        <v>0.2166197700714898</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3191678483702283</v>
+        <v>0.315275557536445</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2340014536958823</v>
+        <v>0.2359014536958823</v>
       </c>
       <c r="C84">
-        <v>-80.67948962978673</v>
+        <v>-85.18411756394642</v>
       </c>
       <c r="D84">
-        <v>133.9865103702133</v>
+        <v>133.0948824360536</v>
       </c>
       <c r="E84">
-        <v>101.866</v>
+        <v>105.479</v>
       </c>
       <c r="F84">
-        <v>296.266</v>
+        <v>299.879</v>
       </c>
       <c r="G84">
         <v>81.59999999999999</v>
@@ -8163,37 +8163,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M84">
-        <v>69.85952280000001</v>
+        <v>70.71146820000001</v>
       </c>
       <c r="N84">
-        <v>-47.83452280000002</v>
+        <v>-48.68646820000002</v>
       </c>
       <c r="O84">
-        <v>-12.3413068824</v>
+        <v>-12.56110879560001</v>
       </c>
       <c r="P84">
-        <v>-35.49321591760001</v>
+        <v>-36.12535940440002</v>
       </c>
       <c r="Q84">
-        <v>-3.89321591760001</v>
+        <v>-4.525359404400014</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3131846790958922</v>
+        <v>0.3289131896309447</v>
       </c>
       <c r="T84">
-        <v>6.175165798981345</v>
+        <v>6.538410845980248</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08134109384440281</v>
+        <v>0.08036108066555457</v>
       </c>
       <c r="W84">
-        <v>0.2166197700714898</v>
+        <v>0.2168508571790622</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.315275557536445</v>
+        <v>0.3114770568432348</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2359014536958823</v>
+        <v>0.2378014536958823</v>
       </c>
       <c r="C85">
-        <v>-85.18411756394642</v>
+        <v>-89.67695707363694</v>
       </c>
       <c r="D85">
-        <v>133.0948824360536</v>
+        <v>132.2150429263631</v>
       </c>
       <c r="E85">
-        <v>105.479</v>
+        <v>109.092</v>
       </c>
       <c r="F85">
-        <v>299.879</v>
+        <v>303.492</v>
       </c>
       <c r="G85">
         <v>81.59999999999999</v>
@@ -8245,37 +8245,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M85">
-        <v>70.71146820000001</v>
+        <v>71.5634136</v>
       </c>
       <c r="N85">
-        <v>-48.68646820000002</v>
+        <v>-49.53841360000001</v>
       </c>
       <c r="O85">
-        <v>-12.56110879560001</v>
+        <v>-12.7809107088</v>
       </c>
       <c r="P85">
-        <v>-36.12535940440002</v>
+        <v>-36.75750289120001</v>
       </c>
       <c r="Q85">
-        <v>-4.525359404400014</v>
+        <v>-5.157502891200004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3289131896309447</v>
+        <v>0.3466077639828788</v>
       </c>
       <c r="T85">
-        <v>6.538410845980248</v>
+        <v>6.947061523854015</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08036108066555457</v>
+        <v>0.07940440113382179</v>
       </c>
       <c r="W85">
-        <v>0.2168508571790622</v>
+        <v>0.2170764422126449</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3114770568432348</v>
+        <v>0.3077689966427201</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2378014536958823</v>
+        <v>0.2397014536958822</v>
       </c>
       <c r="C86">
-        <v>-89.67695707363691</v>
+        <v>-94.15824040987067</v>
       </c>
       <c r="D86">
-        <v>132.2150429263631</v>
+        <v>131.3467595901294</v>
       </c>
       <c r="E86">
-        <v>109.092</v>
+        <v>112.705</v>
       </c>
       <c r="F86">
-        <v>303.492</v>
+        <v>307.105</v>
       </c>
       <c r="G86">
         <v>81.59999999999999</v>
@@ -8327,37 +8327,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M86">
-        <v>71.5634136</v>
+        <v>72.41535900000001</v>
       </c>
       <c r="N86">
-        <v>-49.53841360000001</v>
+        <v>-50.39035900000002</v>
       </c>
       <c r="O86">
-        <v>-12.7809107088</v>
+        <v>-13.00071262200001</v>
       </c>
       <c r="P86">
-        <v>-36.75750289120001</v>
+        <v>-37.38964637800001</v>
       </c>
       <c r="Q86">
-        <v>-5.157502891200004</v>
+        <v>-5.789646378000008</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3466077639828786</v>
+        <v>0.3666616149150705</v>
       </c>
       <c r="T86">
-        <v>6.947061523854011</v>
+        <v>7.410198958777611</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07940440113382179</v>
+        <v>0.078470231708718</v>
       </c>
       <c r="W86">
-        <v>0.2170764422126449</v>
+        <v>0.2172967193630843</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3077689966427201</v>
+        <v>0.3041481849175116</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2397014536958822</v>
+        <v>0.2416014536958822</v>
       </c>
       <c r="C87">
-        <v>-94.15824040987067</v>
+        <v>-98.62819376250465</v>
       </c>
       <c r="D87">
-        <v>131.3467595901294</v>
+        <v>130.4898062374954</v>
       </c>
       <c r="E87">
-        <v>112.705</v>
+        <v>116.318</v>
       </c>
       <c r="F87">
-        <v>307.105</v>
+        <v>310.718</v>
       </c>
       <c r="G87">
         <v>81.59999999999999</v>
@@ -8409,37 +8409,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M87">
-        <v>72.41535900000001</v>
+        <v>73.2673044</v>
       </c>
       <c r="N87">
-        <v>-50.39035900000002</v>
+        <v>-51.24230440000001</v>
       </c>
       <c r="O87">
-        <v>-13.00071262200001</v>
+        <v>-13.2205145352</v>
       </c>
       <c r="P87">
-        <v>-37.38964637800001</v>
+        <v>-38.02178986480001</v>
       </c>
       <c r="Q87">
-        <v>-5.789646378000008</v>
+        <v>-6.421789864800004</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3666616149150705</v>
+        <v>0.3895803016947184</v>
       </c>
       <c r="T87">
-        <v>7.410198958777611</v>
+        <v>7.939498884404584</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.078470231708718</v>
+        <v>0.07755778715396548</v>
       </c>
       <c r="W87">
-        <v>0.2172967193630843</v>
+        <v>0.217511873789095</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3041481849175116</v>
+        <v>0.3006115781161453</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2416014536958822</v>
+        <v>0.2435014536958822</v>
       </c>
       <c r="C88">
-        <v>-98.62819376250465</v>
+        <v>-103.0870374566843</v>
       </c>
       <c r="D88">
-        <v>130.4898062374954</v>
+        <v>129.6439625433157</v>
       </c>
       <c r="E88">
-        <v>116.318</v>
+        <v>119.931</v>
       </c>
       <c r="F88">
-        <v>310.718</v>
+        <v>314.331</v>
       </c>
       <c r="G88">
         <v>81.59999999999999</v>
@@ -8491,37 +8491,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M88">
-        <v>73.2673044</v>
+        <v>74.11924980000001</v>
       </c>
       <c r="N88">
-        <v>-51.24230440000001</v>
+        <v>-52.09424980000001</v>
       </c>
       <c r="O88">
-        <v>-13.2205145352</v>
+        <v>-13.4403164484</v>
       </c>
       <c r="P88">
-        <v>-38.02178986480001</v>
+        <v>-38.65393335160001</v>
       </c>
       <c r="Q88">
-        <v>-6.421789864800004</v>
+        <v>-7.053933351600008</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3895803016947184</v>
+        <v>0.4160249402866198</v>
       </c>
       <c r="T88">
-        <v>7.939498884404584</v>
+        <v>8.55022956782032</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07755778715396548</v>
+        <v>0.07666631833610379</v>
       </c>
       <c r="W88">
-        <v>0.217511873789095</v>
+        <v>0.2177220821363467</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3006115781161453</v>
+        <v>0.2971562726205573</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2435014536958822</v>
+        <v>0.2454014536958823</v>
       </c>
       <c r="C89">
-        <v>-103.0870374566843</v>
+        <v>-107.5349861416969</v>
       </c>
       <c r="D89">
-        <v>129.6439625433157</v>
+        <v>128.8090138583031</v>
       </c>
       <c r="E89">
-        <v>119.931</v>
+        <v>123.544</v>
       </c>
       <c r="F89">
-        <v>314.331</v>
+        <v>317.944</v>
       </c>
       <c r="G89">
         <v>81.59999999999999</v>
@@ -8573,37 +8573,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M89">
-        <v>74.11924980000001</v>
+        <v>74.97119520000001</v>
       </c>
       <c r="N89">
-        <v>-52.09424980000001</v>
+        <v>-52.94619520000002</v>
       </c>
       <c r="O89">
-        <v>-13.4403164484</v>
+        <v>-13.66011836160001</v>
       </c>
       <c r="P89">
-        <v>-38.65393335160001</v>
+        <v>-39.28607683840001</v>
       </c>
       <c r="Q89">
-        <v>-7.053933351600008</v>
+        <v>-7.686076838400012</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4160249402866198</v>
+        <v>0.4468770186438382</v>
       </c>
       <c r="T89">
-        <v>8.55022956782032</v>
+        <v>9.262748698472016</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07666631833610379</v>
+        <v>0.07579511017319353</v>
       </c>
       <c r="W89">
-        <v>0.2177220821363467</v>
+        <v>0.217927513021161</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2971562726205573</v>
+        <v>0.2937794967953237</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2454014536958823</v>
+        <v>0.2473014536958822</v>
       </c>
       <c r="C90">
-        <v>-107.5349861416969</v>
+        <v>-111.9722489725735</v>
       </c>
       <c r="D90">
-        <v>128.8090138583031</v>
+        <v>127.9847510274265</v>
       </c>
       <c r="E90">
-        <v>123.544</v>
+        <v>127.157</v>
       </c>
       <c r="F90">
-        <v>317.944</v>
+        <v>321.557</v>
       </c>
       <c r="G90">
         <v>81.59999999999999</v>
@@ -8655,37 +8655,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M90">
-        <v>74.97119520000001</v>
+        <v>75.8231406</v>
       </c>
       <c r="N90">
-        <v>-52.94619520000002</v>
+        <v>-53.79814060000001</v>
       </c>
       <c r="O90">
-        <v>-13.66011836160001</v>
+        <v>-13.8799202748</v>
       </c>
       <c r="P90">
-        <v>-39.28607683840001</v>
+        <v>-39.91822032520001</v>
       </c>
       <c r="Q90">
-        <v>-7.686076838400012</v>
+        <v>-8.318220325200009</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4468770186438382</v>
+        <v>0.483338565793278</v>
       </c>
       <c r="T90">
-        <v>9.262748698472016</v>
+        <v>10.10481676196947</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07579511017319353</v>
+        <v>0.07494347972180934</v>
       </c>
       <c r="W90">
-        <v>0.217927513021161</v>
+        <v>0.2181283274815974</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2937794967953237</v>
+        <v>0.2904786035729043</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2473014536958822</v>
+        <v>0.2492014536958823</v>
       </c>
       <c r="C91">
-        <v>-111.9722489725735</v>
+        <v>-116.3990297847631</v>
       </c>
       <c r="D91">
-        <v>127.9847510274265</v>
+        <v>127.1709702152369</v>
       </c>
       <c r="E91">
-        <v>127.157</v>
+        <v>130.77</v>
       </c>
       <c r="F91">
-        <v>321.557</v>
+        <v>325.17</v>
       </c>
       <c r="G91">
         <v>81.59999999999999</v>
@@ -8737,37 +8737,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M91">
-        <v>75.8231406</v>
+        <v>76.67508600000001</v>
       </c>
       <c r="N91">
-        <v>-53.79814060000001</v>
+        <v>-54.65008600000002</v>
       </c>
       <c r="O91">
-        <v>-13.8799202748</v>
+        <v>-14.099722188</v>
       </c>
       <c r="P91">
-        <v>-39.91822032520001</v>
+        <v>-40.55036381200001</v>
       </c>
       <c r="Q91">
-        <v>-8.318220325200009</v>
+        <v>-8.950363812000013</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.483338565793278</v>
+        <v>0.5270924223726059</v>
       </c>
       <c r="T91">
-        <v>10.10481676196947</v>
+        <v>11.11529843816642</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07494347972180934</v>
+        <v>0.07411077439156699</v>
       </c>
       <c r="W91">
-        <v>0.2181283274815974</v>
+        <v>0.2183246793984685</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2904786035729043</v>
+        <v>0.2872510635332054</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2492014536958823</v>
+        <v>0.2511014536958823</v>
       </c>
       <c r="C92">
-        <v>-116.3990297847631</v>
+        <v>-120.8155272621843</v>
       </c>
       <c r="D92">
-        <v>127.1709702152369</v>
+        <v>126.3674727378158</v>
       </c>
       <c r="E92">
-        <v>130.77</v>
+        <v>134.383</v>
       </c>
       <c r="F92">
-        <v>325.17</v>
+        <v>328.783</v>
       </c>
       <c r="G92">
         <v>81.59999999999999</v>
@@ -8819,37 +8819,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M92">
-        <v>76.67508600000001</v>
+        <v>77.52703140000001</v>
       </c>
       <c r="N92">
-        <v>-54.65008600000002</v>
+        <v>-55.50203140000002</v>
       </c>
       <c r="O92">
-        <v>-14.099722188</v>
+        <v>-14.31952410120001</v>
       </c>
       <c r="P92">
-        <v>-40.55036381200001</v>
+        <v>-41.18250729880002</v>
       </c>
       <c r="Q92">
-        <v>-8.950363812000013</v>
+        <v>-9.582507298800017</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5270924223726059</v>
+        <v>0.5805693581917843</v>
       </c>
       <c r="T92">
-        <v>11.11529843816642</v>
+        <v>12.35033159796269</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07411077439156699</v>
+        <v>0.07329637027737396</v>
       </c>
       <c r="W92">
-        <v>0.2183246793984685</v>
+        <v>0.2185167158885953</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2872510635332054</v>
+        <v>0.2840944584394339</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2511014536958823</v>
+        <v>0.2530014536958822</v>
       </c>
       <c r="C93">
-        <v>-120.8155272621843</v>
+        <v>-125.2219350989473</v>
       </c>
       <c r="D93">
-        <v>126.3674727378158</v>
+        <v>125.5740649010528</v>
       </c>
       <c r="E93">
-        <v>134.383</v>
+        <v>137.996</v>
       </c>
       <c r="F93">
-        <v>328.783</v>
+        <v>332.396</v>
       </c>
       <c r="G93">
         <v>81.59999999999999</v>
@@ -8901,37 +8901,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M93">
-        <v>77.52703140000001</v>
+        <v>78.3789768</v>
       </c>
       <c r="N93">
-        <v>-55.50203140000002</v>
+        <v>-56.35397680000001</v>
       </c>
       <c r="O93">
-        <v>-14.31952410120001</v>
+        <v>-14.5393260144</v>
       </c>
       <c r="P93">
-        <v>-41.18250729880002</v>
+        <v>-41.81465078560001</v>
       </c>
       <c r="Q93">
-        <v>-9.582507298800017</v>
+        <v>-10.21465078560001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5805693581917843</v>
+        <v>0.6474155279657575</v>
       </c>
       <c r="T93">
-        <v>12.35033159796269</v>
+        <v>13.89412304770803</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07329637027737396</v>
+        <v>0.07249967060044599</v>
       </c>
       <c r="W93">
-        <v>0.2185167158885953</v>
+        <v>0.2187045776724149</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2840944584394339</v>
+        <v>0.281006475195527</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2530014536958822</v>
+        <v>0.2549014536958822</v>
       </c>
       <c r="C94">
-        <v>-125.2219350989473</v>
+        <v>-129.6184421550205</v>
       </c>
       <c r="D94">
-        <v>125.5740649010528</v>
+        <v>124.7905578449795</v>
       </c>
       <c r="E94">
-        <v>137.996</v>
+        <v>141.609</v>
       </c>
       <c r="F94">
-        <v>332.396</v>
+        <v>336.009</v>
       </c>
       <c r="G94">
         <v>81.59999999999999</v>
@@ -8983,37 +8983,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M94">
-        <v>78.3789768</v>
+        <v>79.23092220000001</v>
       </c>
       <c r="N94">
-        <v>-56.35397680000001</v>
+        <v>-57.20592220000002</v>
       </c>
       <c r="O94">
-        <v>-14.5393260144</v>
+        <v>-14.75912792760001</v>
       </c>
       <c r="P94">
-        <v>-41.81465078560001</v>
+        <v>-42.44679427240001</v>
       </c>
       <c r="Q94">
-        <v>-10.21465078560001</v>
+        <v>-10.84679427240001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6474155279657575</v>
+        <v>0.7333606033894372</v>
       </c>
       <c r="T94">
-        <v>13.89412304770803</v>
+        <v>15.87899776880918</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07249967060044599</v>
+        <v>0.07172010424990355</v>
       </c>
       <c r="W94">
-        <v>0.2187045776724149</v>
+        <v>0.2188883994178727</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.281006475195527</v>
+        <v>0.2779849001934246</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2549014536958822</v>
+        <v>0.2568014536958823</v>
       </c>
       <c r="C95">
-        <v>-129.6184421550205</v>
+        <v>-134.0052326061067</v>
       </c>
       <c r="D95">
-        <v>124.7905578449795</v>
+        <v>124.0167673938933</v>
       </c>
       <c r="E95">
-        <v>141.609</v>
+        <v>145.222</v>
       </c>
       <c r="F95">
-        <v>336.009</v>
+        <v>339.622</v>
       </c>
       <c r="G95">
         <v>81.59999999999999</v>
@@ -9065,37 +9065,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M95">
-        <v>79.23092220000001</v>
+        <v>80.0828676</v>
       </c>
       <c r="N95">
-        <v>-57.20592220000002</v>
+        <v>-58.05786760000001</v>
       </c>
       <c r="O95">
-        <v>-14.75912792760001</v>
+        <v>-14.9789298408</v>
       </c>
       <c r="P95">
-        <v>-42.44679427240001</v>
+        <v>-43.0789377592</v>
       </c>
       <c r="Q95">
-        <v>-10.84679427240001</v>
+        <v>-11.4789377592</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7333606033894372</v>
+        <v>0.847954037287677</v>
       </c>
       <c r="T95">
-        <v>15.87899776880918</v>
+        <v>18.52549739694405</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07172010424990355</v>
+        <v>0.07095712441745777</v>
       </c>
       <c r="W95">
-        <v>0.2188883994178727</v>
+        <v>0.2190683100623635</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2779849001934246</v>
+        <v>0.2750276140211542</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2568014536958823</v>
+        <v>0.2587014536958823</v>
       </c>
       <c r="C96">
-        <v>-134.0052326061067</v>
+        <v>-138.3824860879766</v>
       </c>
       <c r="D96">
-        <v>124.0167673938933</v>
+        <v>123.2525139120235</v>
       </c>
       <c r="E96">
-        <v>145.222</v>
+        <v>148.835</v>
       </c>
       <c r="F96">
-        <v>339.622</v>
+        <v>343.235</v>
       </c>
       <c r="G96">
         <v>81.59999999999999</v>
@@ -9147,37 +9147,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M96">
-        <v>80.0828676</v>
+        <v>80.93481300000001</v>
       </c>
       <c r="N96">
-        <v>-58.05786760000001</v>
+        <v>-58.90981300000001</v>
       </c>
       <c r="O96">
-        <v>-14.9789298408</v>
+        <v>-15.198731754</v>
       </c>
       <c r="P96">
-        <v>-43.0789377592</v>
+        <v>-43.71108124600001</v>
       </c>
       <c r="Q96">
-        <v>-11.4789377592</v>
+        <v>-12.111081246</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.847954037287677</v>
+        <v>1.008384844745213</v>
       </c>
       <c r="T96">
-        <v>18.52549739694405</v>
+        <v>22.23059687633287</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07095712441745777</v>
+        <v>0.07021020731832664</v>
       </c>
       <c r="W96">
-        <v>0.2190683100623635</v>
+        <v>0.2192444331143386</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2750276140211542</v>
+        <v>0.2721325865051419</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2587014536958823</v>
+        <v>0.2606014536958823</v>
       </c>
       <c r="C97">
-        <v>-138.3824860879766</v>
+        <v>-142.7503778354984</v>
       </c>
       <c r="D97">
-        <v>123.2525139120235</v>
+        <v>122.4976221645016</v>
       </c>
       <c r="E97">
-        <v>148.835</v>
+        <v>152.448</v>
       </c>
       <c r="F97">
-        <v>343.235</v>
+        <v>346.848</v>
       </c>
       <c r="G97">
         <v>81.59999999999999</v>
@@ -9229,37 +9229,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M97">
-        <v>80.93481300000001</v>
+        <v>81.78675840000001</v>
       </c>
       <c r="N97">
-        <v>-58.90981300000001</v>
+        <v>-59.76175840000002</v>
       </c>
       <c r="O97">
-        <v>-15.198731754</v>
+        <v>-15.41853366720001</v>
       </c>
       <c r="P97">
-        <v>-43.71108124600001</v>
+        <v>-44.34322473280001</v>
       </c>
       <c r="Q97">
-        <v>-12.111081246</v>
+        <v>-12.74322473280001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.008384844745213</v>
+        <v>1.249031055931517</v>
       </c>
       <c r="T97">
-        <v>22.23059687633287</v>
+        <v>27.7882460954161</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07021020731832664</v>
+        <v>0.06947885099209407</v>
       </c>
       <c r="W97">
-        <v>0.2192444331143386</v>
+        <v>0.2194168869360642</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2721325865051419</v>
+        <v>0.2692978720623801</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2606014536958822</v>
+        <v>0.2625014536958822</v>
       </c>
       <c r="C98">
-        <v>-142.7503778354984</v>
+        <v>-147.1090788165907</v>
       </c>
       <c r="D98">
-        <v>122.4976221645016</v>
+        <v>121.7519211834093</v>
       </c>
       <c r="E98">
-        <v>152.448</v>
+        <v>156.061</v>
       </c>
       <c r="F98">
-        <v>346.848</v>
+        <v>350.461</v>
       </c>
       <c r="G98">
         <v>81.59999999999999</v>
@@ -9311,37 +9311,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M98">
-        <v>81.78675840000001</v>
+        <v>82.6387038</v>
       </c>
       <c r="N98">
-        <v>-59.76175840000002</v>
+        <v>-60.61370380000001</v>
       </c>
       <c r="O98">
-        <v>-15.41853366720001</v>
+        <v>-15.6383355804</v>
       </c>
       <c r="P98">
-        <v>-44.34322473280001</v>
+        <v>-44.97536821960001</v>
       </c>
       <c r="Q98">
-        <v>-12.74322473280001</v>
+        <v>-13.37536821960001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.249031055931513</v>
+        <v>1.650108074575351</v>
       </c>
       <c r="T98">
-        <v>27.78824609541602</v>
+        <v>37.05099479388803</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06947885099209407</v>
+        <v>0.06876257417774258</v>
       </c>
       <c r="W98">
-        <v>0.2194168869360642</v>
+        <v>0.2195857850088883</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2692978720623801</v>
+        <v>0.2665216053400875</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2625014536958822</v>
+        <v>0.2644014536958822</v>
       </c>
       <c r="C99">
-        <v>-147.1090788165907</v>
+        <v>-151.4587558613105</v>
       </c>
       <c r="D99">
-        <v>121.7519211834093</v>
+        <v>121.0152441386896</v>
       </c>
       <c r="E99">
-        <v>156.061</v>
+        <v>159.674</v>
       </c>
       <c r="F99">
-        <v>350.461</v>
+        <v>354.074</v>
       </c>
       <c r="G99">
         <v>81.59999999999999</v>
@@ -9393,37 +9393,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M99">
-        <v>82.6387038</v>
+        <v>83.49064920000001</v>
       </c>
       <c r="N99">
-        <v>-60.61370380000001</v>
+        <v>-61.46564920000002</v>
       </c>
       <c r="O99">
-        <v>-15.6383355804</v>
+        <v>-15.8581374936</v>
       </c>
       <c r="P99">
-        <v>-44.97536821960001</v>
+        <v>-45.60751170640001</v>
       </c>
       <c r="Q99">
-        <v>-13.37536821960001</v>
+        <v>-14.00751170640001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.650108074575351</v>
+        <v>2.452262111863027</v>
       </c>
       <c r="T99">
-        <v>37.05099479388803</v>
+        <v>55.57649219083204</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06876257417774258</v>
+        <v>0.06806091525756153</v>
       </c>
       <c r="W99">
-        <v>0.2195857850088883</v>
+        <v>0.219751236182267</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2665216053400875</v>
+        <v>0.2638019971223315</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2644014536958822</v>
+        <v>0.2663014536958822</v>
       </c>
       <c r="C100">
-        <v>-151.4587558613105</v>
+        <v>-155.7995717862841</v>
       </c>
       <c r="D100">
-        <v>121.0152441386896</v>
+        <v>120.2874282137159</v>
       </c>
       <c r="E100">
-        <v>159.674</v>
+        <v>163.287</v>
       </c>
       <c r="F100">
-        <v>354.074</v>
+        <v>357.687</v>
       </c>
       <c r="G100">
         <v>81.59999999999999</v>
@@ -9475,37 +9475,37 @@
         <v>22.02499999999999</v>
       </c>
       <c r="M100">
-        <v>83.49064920000001</v>
+        <v>84.34259460000001</v>
       </c>
       <c r="N100">
-        <v>-61.46564920000002</v>
+        <v>-62.31759460000002</v>
       </c>
       <c r="O100">
-        <v>-15.8581374936</v>
+        <v>-16.07793940680001</v>
       </c>
       <c r="P100">
-        <v>-45.60751170640001</v>
+        <v>-46.23965519320002</v>
       </c>
       <c r="Q100">
-        <v>-14.00751170640001</v>
+        <v>-14.63965519320001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.452262111863027</v>
+        <v>4.858724223726053</v>
       </c>
       <c r="T100">
-        <v>55.57649219083204</v>
+        <v>111.1529843816641</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06806091525756153</v>
+        <v>0.06737343126506092</v>
       </c>
       <c r="W100">
-        <v>0.219751236182267</v>
+        <v>0.2199133449076986</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2638019971223315</v>
+        <v>0.2611373304847322</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2663014536958822</v>
-      </c>
-      <c r="C101">
-        <v>-155.7995717862841</v>
-      </c>
-      <c r="D101">
-        <v>120.2874282137159</v>
-      </c>
-      <c r="E101">
-        <v>163.287</v>
-      </c>
-      <c r="F101">
-        <v>357.687</v>
-      </c>
-      <c r="G101">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="H101">
-        <v>166.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>53.62499999999999</v>
-      </c>
-      <c r="K101">
-        <v>31.6</v>
-      </c>
-      <c r="L101">
-        <v>22.02499999999999</v>
-      </c>
-      <c r="M101">
-        <v>84.34259460000001</v>
-      </c>
-      <c r="N101">
-        <v>-62.31759460000002</v>
-      </c>
-      <c r="O101">
-        <v>-16.07793940680001</v>
-      </c>
-      <c r="P101">
-        <v>-46.23965519320002</v>
-      </c>
-      <c r="Q101">
-        <v>-14.63965519320001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.858724223726053</v>
-      </c>
-      <c r="T101">
-        <v>111.1529843816641</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06737343126506092</v>
-      </c>
-      <c r="W101">
-        <v>0.2199133449076986</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2611373304847322</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
